--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1850,6 +1850,4161 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129433719</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78446</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>470105</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7023529</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129438295</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91507</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>470035</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7023758</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129436988</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92498</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>470069</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7023735</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129438342</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98710</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>470019</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7023755</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129436901</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>470084</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7023711</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Barkflag på gran</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129438250</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91316</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>470035</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7023758</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129433401</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>470063</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7023544</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129438622</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91507</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>469988</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7023785</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129438563</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>469981</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7023772</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129438355</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98710</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>470019</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7023756</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129432686</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>469936</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7023512</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129433226</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91316</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>470038</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7023552</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129438443</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>469996</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7023753</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129431892</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91507</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>469888</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7023489</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129432713</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97581</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>469891</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7023526</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Mkt rikligt</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129438822</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92498</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>469982</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7023799</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129439057</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91563</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>470060</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7023719</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129431802</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57568</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>469884</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7023463</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Höstläte.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129432249</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92498</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>469890</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7023461</v>
+      </c>
+      <c r="S31" t="n">
+        <v>30</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129432736</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91543</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>469874</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7023510</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129436692</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91539</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>470084</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7023711</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129437246</v>
+      </c>
+      <c r="B34" t="n">
+        <v>92498</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>470062</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7023744</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129435273</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>470105</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7023529</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129432551</v>
+      </c>
+      <c r="B36" t="n">
+        <v>83003</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>308</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>469918</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7023461</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På björkstubbe.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129433427</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98627</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>470059</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7023547</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129438312</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98710</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>470030</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7023735</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129433664</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>470092</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7023517</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Bearbetad torraka.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129437140</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>470060</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7023746</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129431850</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>469888</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7023489</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129438474</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>469996</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7023753</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Barkflag/ringhack</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129433079</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78446</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>469974</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7023561</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129433203</v>
+      </c>
+      <c r="B44" t="n">
+        <v>105759</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>470028</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7023556</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129431867</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58360</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>102125</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tallbit</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Pinicola enucleator</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>469888</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7023489</v>
+      </c>
+      <c r="S45" t="n">
+        <v>50</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Lock.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129438495</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91543</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>470000</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7023770</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129432587</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98614</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>469915</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7023493</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129438794</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91543</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>469986</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7023830</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129437030</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>470069</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7023735</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -4303,10 +4303,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129435273</v>
+        <v>129432551</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>83003</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4314,39 +4314,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>470105</v>
+        <v>469918</v>
       </c>
       <c r="R35" t="n">
-        <v>7023529</v>
+        <v>7023461</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4378,7 +4373,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4388,7 +4383,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På björkstubbe.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4415,10 +4415,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129432551</v>
+        <v>129435273</v>
       </c>
       <c r="B36" t="n">
-        <v>83003</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4426,34 +4426,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>469918</v>
+        <v>470105</v>
       </c>
       <c r="R36" t="n">
-        <v>7023461</v>
+        <v>7023529</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4485,7 +4490,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4495,12 +4500,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På björkstubbe.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -1855,7 +1855,7 @@
         <v>129433719</v>
       </c>
       <c r="B13" t="n">
-        <v>78446</v>
+        <v>78447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129438295</v>
       </c>
       <c r="B14" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>129436988</v>
       </c>
       <c r="B15" t="n">
-        <v>92498</v>
+        <v>92500</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>129438342</v>
       </c>
       <c r="B16" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,50 +2289,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129436901</v>
+        <v>129438250</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>91318</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470084</v>
+        <v>470035</v>
       </c>
       <c r="R17" t="n">
-        <v>7023711</v>
+        <v>7023758</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2364,7 +2359,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2374,12 +2369,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Barkflag på gran</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,45 +2396,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129438250</v>
+        <v>129436901</v>
       </c>
       <c r="B18" t="n">
-        <v>91316</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3215</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>470035</v>
+        <v>470084</v>
       </c>
       <c r="R18" t="n">
-        <v>7023758</v>
+        <v>7023711</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2476,7 +2471,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2486,7 +2481,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Barkflag på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,7 +2632,7 @@
         <v>129438622</v>
       </c>
       <c r="B20" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129438563</v>
+        <v>129432686</v>
       </c>
       <c r="B21" t="n">
         <v>57887</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469981</v>
+        <v>469936</v>
       </c>
       <c r="R21" t="n">
-        <v>7023772</v>
+        <v>7023512</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2852,42 +2852,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129438355</v>
+        <v>129438563</v>
       </c>
       <c r="B22" t="n">
-        <v>98710</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2896,13 +2896,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>470019</v>
+        <v>469981</v>
       </c>
       <c r="R22" t="n">
-        <v>7023756</v>
+        <v>7023772</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2968,42 +2968,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129432686</v>
+        <v>129438355</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>98712</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3012,13 +3012,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469936</v>
+        <v>470019</v>
       </c>
       <c r="R23" t="n">
-        <v>7023512</v>
+        <v>7023756</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3087,7 +3087,7 @@
         <v>129433226</v>
       </c>
       <c r="B24" t="n">
-        <v>91316</v>
+        <v>91318</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3191,54 +3191,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129438443</v>
+        <v>129431892</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>91509</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>469996</v>
+        <v>469888</v>
       </c>
       <c r="R25" t="n">
-        <v>7023753</v>
+        <v>7023489</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3270,7 +3261,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3280,7 +3271,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3307,45 +3298,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129431892</v>
+        <v>129438443</v>
       </c>
       <c r="B26" t="n">
-        <v>91507</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>469888</v>
+        <v>469996</v>
       </c>
       <c r="R26" t="n">
-        <v>7023489</v>
+        <v>7023753</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3377,7 +3377,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3417,7 +3417,7 @@
         <v>129432713</v>
       </c>
       <c r="B27" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>129438822</v>
       </c>
       <c r="B28" t="n">
-        <v>92498</v>
+        <v>92500</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3642,30 +3642,34 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129439057</v>
+        <v>129432249</v>
       </c>
       <c r="B29" t="n">
-        <v>91563</v>
+        <v>92500</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3673,13 +3677,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>470060</v>
+        <v>469890</v>
       </c>
       <c r="R29" t="n">
-        <v>7023719</v>
+        <v>7023461</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3708,7 +3712,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3718,7 +3722,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3745,54 +3749,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129431802</v>
+        <v>129432736</v>
       </c>
       <c r="B30" t="n">
-        <v>57568</v>
+        <v>91545</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102621</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469884</v>
+        <v>469874</v>
       </c>
       <c r="R30" t="n">
-        <v>7023463</v>
+        <v>7023510</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3824,7 +3819,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3834,12 +3829,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:26</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Höstläte.</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3866,34 +3856,30 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129432249</v>
+        <v>129439057</v>
       </c>
       <c r="B31" t="n">
-        <v>92498</v>
+        <v>91565</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3901,13 +3887,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469890</v>
+        <v>470060</v>
       </c>
       <c r="R31" t="n">
-        <v>7023461</v>
+        <v>7023719</v>
       </c>
       <c r="S31" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3936,7 +3922,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3946,7 +3932,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3973,45 +3959,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129432736</v>
+        <v>129431802</v>
       </c>
       <c r="B32" t="n">
-        <v>91543</v>
+        <v>57568</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>102621</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>469874</v>
+        <v>469884</v>
       </c>
       <c r="R32" t="n">
-        <v>7023510</v>
+        <v>7023463</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4043,7 +4038,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4053,7 +4048,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Höstläte.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4080,54 +4080,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129436692</v>
+        <v>129437246</v>
       </c>
       <c r="B33" t="n">
-        <v>91539</v>
+        <v>92500</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>470084</v>
+        <v>470062</v>
       </c>
       <c r="R33" t="n">
-        <v>7023711</v>
+        <v>7023744</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4159,7 +4150,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4169,7 +4160,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4196,45 +4187,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129437246</v>
+        <v>129436692</v>
       </c>
       <c r="B34" t="n">
-        <v>92498</v>
+        <v>91541</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>470062</v>
+        <v>470084</v>
       </c>
       <c r="R34" t="n">
-        <v>7023744</v>
+        <v>7023711</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4303,10 +4303,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129432551</v>
+        <v>129435273</v>
       </c>
       <c r="B35" t="n">
-        <v>83003</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4314,34 +4314,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>469918</v>
+        <v>470105</v>
       </c>
       <c r="R35" t="n">
-        <v>7023461</v>
+        <v>7023529</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4373,7 +4378,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4383,12 +4388,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På björkstubbe.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4415,10 +4415,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129435273</v>
+        <v>129432551</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>83004</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4426,39 +4426,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>470105</v>
+        <v>469918</v>
       </c>
       <c r="R36" t="n">
-        <v>7023529</v>
+        <v>7023461</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4490,7 +4485,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4500,7 +4495,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På björkstubbe.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4530,7 +4530,7 @@
         <v>129433427</v>
       </c>
       <c r="B37" t="n">
-        <v>98627</v>
+        <v>98629</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>129438312</v>
       </c>
       <c r="B38" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4988,10 +4988,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129431850</v>
+        <v>129433079</v>
       </c>
       <c r="B41" t="n">
-        <v>57887</v>
+        <v>78447</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4999,51 +4999,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>469888</v>
+        <v>469974</v>
       </c>
       <c r="R41" t="n">
-        <v>7023489</v>
+        <v>7023561</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5072,7 +5058,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5082,7 +5068,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5226,10 +5212,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129433079</v>
+        <v>129431850</v>
       </c>
       <c r="B43" t="n">
-        <v>78446</v>
+        <v>57887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5237,37 +5223,51 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>469974</v>
+        <v>469888</v>
       </c>
       <c r="R43" t="n">
-        <v>7023561</v>
+        <v>7023489</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5336,7 +5336,7 @@
         <v>129433203</v>
       </c>
       <c r="B44" t="n">
-        <v>105759</v>
+        <v>105761</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v>129438495</v>
       </c>
       <c r="B46" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>129432587</v>
       </c>
       <c r="B47" t="n">
-        <v>98614</v>
+        <v>98616</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5793,10 +5793,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129438794</v>
+        <v>129437030</v>
       </c>
       <c r="B48" t="n">
-        <v>91543</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5804,21 +5804,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>469986</v>
+        <v>470069</v>
       </c>
       <c r="R48" t="n">
-        <v>7023830</v>
+        <v>7023735</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5900,10 +5900,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129437030</v>
+        <v>129438794</v>
       </c>
       <c r="B49" t="n">
-        <v>79043</v>
+        <v>91545</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5911,21 +5911,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>470069</v>
+        <v>469986</v>
       </c>
       <c r="R49" t="n">
-        <v>7023735</v>
+        <v>7023830</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -1852,32 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129433719</v>
+        <v>129438295</v>
       </c>
       <c r="B13" t="n">
-        <v>78447</v>
+        <v>91513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470105</v>
+        <v>470035</v>
       </c>
       <c r="R13" t="n">
-        <v>7023529</v>
+        <v>7023758</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,32 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129438295</v>
+        <v>129433719</v>
       </c>
       <c r="B14" t="n">
-        <v>91509</v>
+        <v>78447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470035</v>
+        <v>470105</v>
       </c>
       <c r="R14" t="n">
-        <v>7023758</v>
+        <v>7023529</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,7 +2069,7 @@
         <v>129436988</v>
       </c>
       <c r="B15" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>129438342</v>
       </c>
       <c r="B16" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,45 +2289,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129438250</v>
+        <v>129436901</v>
       </c>
       <c r="B17" t="n">
-        <v>91318</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3215</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470035</v>
+        <v>470084</v>
       </c>
       <c r="R17" t="n">
-        <v>7023758</v>
+        <v>7023711</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,7 +2364,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2369,7 +2374,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Barkflag på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2396,50 +2406,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129436901</v>
+        <v>129438250</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>91322</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>470084</v>
+        <v>470035</v>
       </c>
       <c r="R18" t="n">
-        <v>7023711</v>
+        <v>7023758</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2471,7 +2476,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2481,12 +2486,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Barkflag på gran</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,7 +2632,7 @@
         <v>129438622</v>
       </c>
       <c r="B20" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,54 +2736,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129432686</v>
+        <v>129433226</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>91322</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>3215</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469936</v>
+        <v>470038</v>
       </c>
       <c r="R21" t="n">
-        <v>7023512</v>
+        <v>7023552</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2815,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2825,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2852,7 +2843,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129438563</v>
+        <v>129432686</v>
       </c>
       <c r="B22" t="n">
         <v>57887</v>
@@ -2882,7 +2873,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2896,10 +2887,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469981</v>
+        <v>469936</v>
       </c>
       <c r="R22" t="n">
-        <v>7023772</v>
+        <v>7023512</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2931,7 +2922,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2941,7 +2932,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2968,42 +2959,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129438355</v>
+        <v>129438563</v>
       </c>
       <c r="B23" t="n">
-        <v>98712</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3012,13 +3003,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>470019</v>
+        <v>469981</v>
       </c>
       <c r="R23" t="n">
-        <v>7023756</v>
+        <v>7023772</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3047,7 +3038,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3057,7 +3048,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3084,48 +3075,57 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129433226</v>
+        <v>129438355</v>
       </c>
       <c r="B24" t="n">
-        <v>91318</v>
+        <v>98716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>470038</v>
+        <v>470019</v>
       </c>
       <c r="R24" t="n">
-        <v>7023552</v>
+        <v>7023756</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3191,10 +3191,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129431892</v>
+        <v>129432713</v>
       </c>
       <c r="B25" t="n">
-        <v>91509</v>
+        <v>97587</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3202,34 +3202,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>469888</v>
+        <v>469891</v>
       </c>
       <c r="R25" t="n">
-        <v>7023489</v>
+        <v>7023526</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3261,7 +3270,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3271,7 +3280,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Mkt rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3298,54 +3312,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129438443</v>
+        <v>129431892</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>91513</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>469996</v>
+        <v>469888</v>
       </c>
       <c r="R26" t="n">
-        <v>7023753</v>
+        <v>7023489</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3377,7 +3382,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3387,7 +3392,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3414,42 +3419,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129432713</v>
+        <v>129438443</v>
       </c>
       <c r="B27" t="n">
-        <v>97583</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3458,10 +3463,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469891</v>
+        <v>469996</v>
       </c>
       <c r="R27" t="n">
-        <v>7023526</v>
+        <v>7023753</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3493,7 +3498,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3503,12 +3508,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Mkt rikligt</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3538,7 +3538,7 @@
         <v>129438822</v>
       </c>
       <c r="B28" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3642,34 +3642,30 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129432249</v>
+        <v>129439057</v>
       </c>
       <c r="B29" t="n">
-        <v>92500</v>
+        <v>91569</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3677,13 +3673,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469890</v>
+        <v>470060</v>
       </c>
       <c r="R29" t="n">
-        <v>7023461</v>
+        <v>7023719</v>
       </c>
       <c r="S29" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3712,7 +3708,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3722,7 +3718,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3749,32 +3745,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129432736</v>
+        <v>129432249</v>
       </c>
       <c r="B30" t="n">
-        <v>91545</v>
+        <v>92504</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3784,13 +3780,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469874</v>
+        <v>469890</v>
       </c>
       <c r="R30" t="n">
-        <v>7023510</v>
+        <v>7023461</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3819,7 +3815,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3829,7 +3825,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3856,10 +3852,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129439057</v>
+        <v>129432736</v>
       </c>
       <c r="B31" t="n">
-        <v>91565</v>
+        <v>91549</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3867,19 +3863,23 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>470060</v>
+        <v>469874</v>
       </c>
       <c r="R31" t="n">
-        <v>7023719</v>
+        <v>7023510</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4080,45 +4080,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129437246</v>
+        <v>129436692</v>
       </c>
       <c r="B33" t="n">
-        <v>92500</v>
+        <v>91545</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>470062</v>
+        <v>470084</v>
       </c>
       <c r="R33" t="n">
-        <v>7023744</v>
+        <v>7023711</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4150,7 +4159,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4160,7 +4169,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4187,54 +4196,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129436692</v>
+        <v>129437246</v>
       </c>
       <c r="B34" t="n">
-        <v>91541</v>
+        <v>92504</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>470084</v>
+        <v>470062</v>
       </c>
       <c r="R34" t="n">
-        <v>7023711</v>
+        <v>7023744</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4303,10 +4303,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129435273</v>
+        <v>129432551</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>83004</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4314,39 +4314,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>470105</v>
+        <v>469918</v>
       </c>
       <c r="R35" t="n">
-        <v>7023529</v>
+        <v>7023461</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4378,7 +4373,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4388,7 +4383,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På björkstubbe.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4415,10 +4415,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129432551</v>
+        <v>129435273</v>
       </c>
       <c r="B36" t="n">
-        <v>83004</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4426,34 +4426,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>469918</v>
+        <v>470105</v>
       </c>
       <c r="R36" t="n">
-        <v>7023461</v>
+        <v>7023529</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4485,7 +4490,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4495,12 +4500,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På björkstubbe.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4530,7 +4530,7 @@
         <v>129433427</v>
       </c>
       <c r="B37" t="n">
-        <v>98629</v>
+        <v>98633</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>129438312</v>
       </c>
       <c r="B38" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129433664</v>
+        <v>129437140</v>
       </c>
       <c r="B39" t="n">
         <v>57724</v>
@@ -4799,13 +4799,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>470092</v>
+        <v>470060</v>
       </c>
       <c r="R39" t="n">
-        <v>7023517</v>
+        <v>7023746</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4844,12 +4844,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Bearbetad torraka.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4876,7 +4871,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129437140</v>
+        <v>129433664</v>
       </c>
       <c r="B40" t="n">
         <v>57724</v>
@@ -4916,13 +4911,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>470060</v>
+        <v>470092</v>
       </c>
       <c r="R40" t="n">
-        <v>7023746</v>
+        <v>7023517</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4951,7 +4946,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4961,7 +4956,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Bearbetad torraka.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4988,10 +4988,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129433079</v>
+        <v>129438474</v>
       </c>
       <c r="B41" t="n">
-        <v>78447</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4999,37 +4999,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>469974</v>
+        <v>469996</v>
       </c>
       <c r="R41" t="n">
-        <v>7023561</v>
+        <v>7023753</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5058,7 +5063,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5068,7 +5073,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Barkflag/ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5095,10 +5105,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129438474</v>
+        <v>129431850</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5106,27 +5116,36 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5135,10 +5154,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469996</v>
+        <v>469888</v>
       </c>
       <c r="R42" t="n">
-        <v>7023753</v>
+        <v>7023489</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5170,7 +5189,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5180,12 +5199,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Barkflag/ringhack</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5212,10 +5226,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129431850</v>
+        <v>129433079</v>
       </c>
       <c r="B43" t="n">
-        <v>57887</v>
+        <v>78447</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5223,51 +5237,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>469888</v>
+        <v>469974</v>
       </c>
       <c r="R43" t="n">
-        <v>7023489</v>
+        <v>7023561</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5336,7 +5336,7 @@
         <v>129433203</v>
       </c>
       <c r="B44" t="n">
-        <v>105761</v>
+        <v>105765</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5570,45 +5570,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129438495</v>
+        <v>129432587</v>
       </c>
       <c r="B46" t="n">
-        <v>91545</v>
+        <v>98620</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>220093</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>470000</v>
+        <v>469915</v>
       </c>
       <c r="R46" t="n">
-        <v>7023770</v>
+        <v>7023493</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5640,7 +5649,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5650,7 +5659,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5677,54 +5686,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129432587</v>
+        <v>129438495</v>
       </c>
       <c r="B47" t="n">
-        <v>98616</v>
+        <v>91549</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220093</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>469915</v>
+        <v>470000</v>
       </c>
       <c r="R47" t="n">
-        <v>7023493</v>
+        <v>7023770</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5793,10 +5793,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129437030</v>
+        <v>129438794</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>91549</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5804,21 +5804,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>470069</v>
+        <v>469986</v>
       </c>
       <c r="R48" t="n">
-        <v>7023735</v>
+        <v>7023830</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5900,10 +5900,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129438794</v>
+        <v>129437030</v>
       </c>
       <c r="B49" t="n">
-        <v>91545</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5911,21 +5911,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>469986</v>
+        <v>470069</v>
       </c>
       <c r="R49" t="n">
-        <v>7023830</v>
+        <v>7023735</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1855,7 +1855,7 @@
         <v>129438295</v>
       </c>
       <c r="B13" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>129436988</v>
       </c>
       <c r="B15" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,54 +2173,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129438342</v>
+        <v>129438250</v>
       </c>
       <c r="B16" t="n">
-        <v>98716</v>
+        <v>91323</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470019</v>
+        <v>470035</v>
       </c>
       <c r="R16" t="n">
-        <v>7023755</v>
+        <v>7023758</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2262,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,45 +2397,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129438250</v>
+        <v>129438342</v>
       </c>
       <c r="B18" t="n">
-        <v>91322</v>
+        <v>98724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>470035</v>
+        <v>470019</v>
       </c>
       <c r="R18" t="n">
-        <v>7023758</v>
+        <v>7023755</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2629,45 +2629,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129438622</v>
+        <v>129438355</v>
       </c>
       <c r="B20" t="n">
-        <v>91513</v>
+        <v>98724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469988</v>
+        <v>470019</v>
       </c>
       <c r="R20" t="n">
-        <v>7023785</v>
+        <v>7023756</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,7 +2708,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2709,7 +2718,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2739,7 +2748,7 @@
         <v>129433226</v>
       </c>
       <c r="B21" t="n">
-        <v>91322</v>
+        <v>91323</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,57 +2852,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129432686</v>
+        <v>129438622</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>91514</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469936</v>
+        <v>469988</v>
       </c>
       <c r="R22" t="n">
-        <v>7023512</v>
+        <v>7023785</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2959,7 +2959,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129438563</v>
+        <v>129432686</v>
       </c>
       <c r="B23" t="n">
         <v>57887</v>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3003,10 +3003,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469981</v>
+        <v>469936</v>
       </c>
       <c r="R23" t="n">
-        <v>7023772</v>
+        <v>7023512</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3075,42 +3075,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129438355</v>
+        <v>129438563</v>
       </c>
       <c r="B24" t="n">
-        <v>98716</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3119,13 +3119,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>470019</v>
+        <v>469981</v>
       </c>
       <c r="R24" t="n">
-        <v>7023756</v>
+        <v>7023772</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3191,10 +3191,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129432713</v>
+        <v>129431892</v>
       </c>
       <c r="B25" t="n">
-        <v>97587</v>
+        <v>91514</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3202,43 +3202,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>469891</v>
+        <v>469888</v>
       </c>
       <c r="R25" t="n">
-        <v>7023526</v>
+        <v>7023489</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3270,7 +3261,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3280,12 +3271,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Mkt rikligt</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3312,45 +3298,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129431892</v>
+        <v>129438443</v>
       </c>
       <c r="B26" t="n">
-        <v>91513</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>469888</v>
+        <v>469996</v>
       </c>
       <c r="R26" t="n">
-        <v>7023489</v>
+        <v>7023753</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3382,7 +3377,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3392,7 +3387,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3419,42 +3414,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129438443</v>
+        <v>129432713</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>97595</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3463,10 +3458,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469996</v>
+        <v>469891</v>
       </c>
       <c r="R27" t="n">
-        <v>7023753</v>
+        <v>7023526</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3498,7 +3493,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3508,7 +3503,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Mkt rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3538,7 +3538,7 @@
         <v>129438822</v>
       </c>
       <c r="B28" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>129439057</v>
       </c>
       <c r="B29" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>129432249</v>
       </c>
       <c r="B30" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3852,45 +3852,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129432736</v>
+        <v>129431802</v>
       </c>
       <c r="B31" t="n">
-        <v>91549</v>
+        <v>57568</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>102621</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469874</v>
+        <v>469884</v>
       </c>
       <c r="R31" t="n">
-        <v>7023510</v>
+        <v>7023463</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3922,7 +3931,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3932,7 +3941,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Höstläte.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3959,54 +3973,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129431802</v>
+        <v>129432736</v>
       </c>
       <c r="B32" t="n">
-        <v>57568</v>
+        <v>91550</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102621</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>469884</v>
+        <v>469874</v>
       </c>
       <c r="R32" t="n">
-        <v>7023463</v>
+        <v>7023510</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4038,7 +4043,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4048,12 +4053,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:26</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Höstläte.</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4083,7 +4083,7 @@
         <v>129436692</v>
       </c>
       <c r="B33" t="n">
-        <v>91545</v>
+        <v>91546</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>129437246</v>
       </c>
       <c r="B34" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>129433427</v>
       </c>
       <c r="B37" t="n">
-        <v>98633</v>
+        <v>98641</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>129438312</v>
       </c>
       <c r="B38" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129437140</v>
+        <v>129433664</v>
       </c>
       <c r="B39" t="n">
         <v>57724</v>
@@ -4799,13 +4799,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>470060</v>
+        <v>470092</v>
       </c>
       <c r="R39" t="n">
-        <v>7023746</v>
+        <v>7023517</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4844,7 +4844,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Bearbetad torraka.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4871,7 +4876,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129433664</v>
+        <v>129437140</v>
       </c>
       <c r="B40" t="n">
         <v>57724</v>
@@ -4911,13 +4916,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>470092</v>
+        <v>470060</v>
       </c>
       <c r="R40" t="n">
-        <v>7023517</v>
+        <v>7023746</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4946,7 +4951,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4956,12 +4961,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Bearbetad torraka.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4988,10 +4988,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129438474</v>
+        <v>129433079</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>78447</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4999,42 +4999,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>469996</v>
+        <v>469974</v>
       </c>
       <c r="R41" t="n">
-        <v>7023753</v>
+        <v>7023561</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5063,7 +5058,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5073,12 +5068,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Barkflag/ringhack</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5105,10 +5095,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129431850</v>
+        <v>129438474</v>
       </c>
       <c r="B42" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5116,36 +5106,27 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5154,10 +5135,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469888</v>
+        <v>469996</v>
       </c>
       <c r="R42" t="n">
-        <v>7023489</v>
+        <v>7023753</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5189,7 +5170,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5199,7 +5180,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Barkflag/ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5226,10 +5212,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129433079</v>
+        <v>129431850</v>
       </c>
       <c r="B43" t="n">
-        <v>78447</v>
+        <v>57887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5237,37 +5223,51 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>469974</v>
+        <v>469888</v>
       </c>
       <c r="R43" t="n">
-        <v>7023561</v>
+        <v>7023489</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5336,7 +5336,7 @@
         <v>129433203</v>
       </c>
       <c r="B44" t="n">
-        <v>105765</v>
+        <v>105775</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v>129432587</v>
       </c>
       <c r="B46" t="n">
-        <v>98620</v>
+        <v>98628</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>129438495</v>
       </c>
       <c r="B47" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5793,10 +5793,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129438794</v>
+        <v>129437030</v>
       </c>
       <c r="B48" t="n">
-        <v>91549</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5804,21 +5804,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>469986</v>
+        <v>470069</v>
       </c>
       <c r="R48" t="n">
-        <v>7023830</v>
+        <v>7023735</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5900,10 +5900,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129437030</v>
+        <v>129438794</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5911,21 +5911,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>470069</v>
+        <v>469986</v>
       </c>
       <c r="R49" t="n">
-        <v>7023735</v>
+        <v>7023830</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6004,6 +6004,113 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129432731</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91550</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Svintjärnflon, Svintjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>469875</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7023508</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -2629,54 +2629,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129438355</v>
+        <v>129438622</v>
       </c>
       <c r="B20" t="n">
-        <v>98724</v>
+        <v>91514</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>470019</v>
+        <v>469988</v>
       </c>
       <c r="R20" t="n">
-        <v>7023756</v>
+        <v>7023785</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2708,7 +2699,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2718,7 +2709,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2852,48 +2843,57 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129438622</v>
+        <v>129432686</v>
       </c>
       <c r="B22" t="n">
-        <v>91514</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469988</v>
+        <v>469936</v>
       </c>
       <c r="R22" t="n">
-        <v>7023785</v>
+        <v>7023512</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2959,7 +2959,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129432686</v>
+        <v>129438563</v>
       </c>
       <c r="B23" t="n">
         <v>57887</v>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3003,10 +3003,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469936</v>
+        <v>469981</v>
       </c>
       <c r="R23" t="n">
-        <v>7023512</v>
+        <v>7023772</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3075,42 +3075,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129438563</v>
+        <v>129438355</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>98724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3119,13 +3119,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>469981</v>
+        <v>470019</v>
       </c>
       <c r="R24" t="n">
-        <v>7023772</v>
+        <v>7023756</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3191,45 +3191,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129431892</v>
+        <v>129438443</v>
       </c>
       <c r="B25" t="n">
-        <v>91514</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>469888</v>
+        <v>469996</v>
       </c>
       <c r="R25" t="n">
-        <v>7023489</v>
+        <v>7023753</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3261,7 +3270,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3271,7 +3280,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3298,42 +3307,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129438443</v>
+        <v>129432713</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>97595</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3342,10 +3351,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>469996</v>
+        <v>469891</v>
       </c>
       <c r="R26" t="n">
-        <v>7023753</v>
+        <v>7023526</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3377,7 +3386,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3387,7 +3396,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Mkt rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3414,10 +3428,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129432713</v>
+        <v>129431892</v>
       </c>
       <c r="B27" t="n">
-        <v>97595</v>
+        <v>91514</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3425,43 +3439,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469891</v>
+        <v>469888</v>
       </c>
       <c r="R27" t="n">
-        <v>7023526</v>
+        <v>7023489</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3493,7 +3498,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3503,12 +3508,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Mkt rikligt</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3852,54 +3852,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129431802</v>
+        <v>129432736</v>
       </c>
       <c r="B31" t="n">
-        <v>57568</v>
+        <v>91550</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102621</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469884</v>
+        <v>469874</v>
       </c>
       <c r="R31" t="n">
-        <v>7023463</v>
+        <v>7023510</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3931,7 +3922,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3941,12 +3932,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:26</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Höstläte.</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3973,45 +3959,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129432736</v>
+        <v>129431802</v>
       </c>
       <c r="B32" t="n">
-        <v>91550</v>
+        <v>57568</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>102621</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>469874</v>
+        <v>469884</v>
       </c>
       <c r="R32" t="n">
-        <v>7023510</v>
+        <v>7023463</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4043,7 +4038,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4053,7 +4048,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Höstläte.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4988,10 +4988,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129433079</v>
+        <v>129438474</v>
       </c>
       <c r="B41" t="n">
-        <v>78447</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4999,37 +4999,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>469974</v>
+        <v>469996</v>
       </c>
       <c r="R41" t="n">
-        <v>7023561</v>
+        <v>7023753</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5058,7 +5063,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5068,7 +5073,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Barkflag/ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5095,10 +5105,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129438474</v>
+        <v>129433079</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>78447</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5106,42 +5116,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469996</v>
+        <v>469974</v>
       </c>
       <c r="R42" t="n">
-        <v>7023753</v>
+        <v>7023561</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5170,7 +5175,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5180,12 +5185,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Barkflag/ringhack</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5570,54 +5570,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129432587</v>
+        <v>129438495</v>
       </c>
       <c r="B46" t="n">
-        <v>98628</v>
+        <v>91550</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220093</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>469915</v>
+        <v>470000</v>
       </c>
       <c r="R46" t="n">
-        <v>7023493</v>
+        <v>7023770</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5649,7 +5640,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5659,7 +5650,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5686,45 +5677,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129438495</v>
+        <v>129432587</v>
       </c>
       <c r="B47" t="n">
-        <v>91550</v>
+        <v>98628</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>220093</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>470000</v>
+        <v>469915</v>
       </c>
       <c r="R47" t="n">
-        <v>7023770</v>
+        <v>7023493</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -3745,10 +3745,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129432249</v>
+        <v>129431802</v>
       </c>
       <c r="B30" t="n">
-        <v>92505</v>
+        <v>57568</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,37 +3756,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4769</v>
+        <v>102621</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469890</v>
+        <v>469884</v>
       </c>
       <c r="R30" t="n">
-        <v>7023461</v>
+        <v>7023463</v>
       </c>
       <c r="S30" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3815,7 +3824,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3825,7 +3834,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Höstläte.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3852,32 +3866,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129432736</v>
+        <v>129432249</v>
       </c>
       <c r="B31" t="n">
-        <v>91550</v>
+        <v>92505</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3887,13 +3901,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469874</v>
+        <v>469890</v>
       </c>
       <c r="R31" t="n">
-        <v>7023510</v>
+        <v>7023461</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3922,7 +3936,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3932,7 +3946,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3959,54 +3973,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129431802</v>
+        <v>129432736</v>
       </c>
       <c r="B32" t="n">
-        <v>57568</v>
+        <v>91550</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102621</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>469884</v>
+        <v>469874</v>
       </c>
       <c r="R32" t="n">
-        <v>7023463</v>
+        <v>7023510</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4038,7 +4043,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4048,12 +4053,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:26</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Höstläte.</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4988,10 +4988,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129438474</v>
+        <v>129433079</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>78447</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4999,42 +4999,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>469996</v>
+        <v>469974</v>
       </c>
       <c r="R41" t="n">
-        <v>7023753</v>
+        <v>7023561</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5063,7 +5058,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5073,12 +5068,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Barkflag/ringhack</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5105,10 +5095,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129433079</v>
+        <v>129438474</v>
       </c>
       <c r="B42" t="n">
-        <v>78447</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5116,37 +5106,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469974</v>
+        <v>469996</v>
       </c>
       <c r="R42" t="n">
-        <v>7023561</v>
+        <v>7023753</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5175,7 +5170,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5185,7 +5180,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Barkflag/ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -1852,32 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129438295</v>
+        <v>129433719</v>
       </c>
       <c r="B13" t="n">
-        <v>91514</v>
+        <v>78447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470035</v>
+        <v>470105</v>
       </c>
       <c r="R13" t="n">
-        <v>7023758</v>
+        <v>7023529</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,32 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129433719</v>
+        <v>129438295</v>
       </c>
       <c r="B14" t="n">
-        <v>78447</v>
+        <v>91517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470105</v>
+        <v>470035</v>
       </c>
       <c r="R14" t="n">
-        <v>7023529</v>
+        <v>7023758</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,7 +2069,7 @@
         <v>129436988</v>
       </c>
       <c r="B15" t="n">
-        <v>92505</v>
+        <v>92508</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>129438250</v>
       </c>
       <c r="B16" t="n">
-        <v>91323</v>
+        <v>91326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>129438342</v>
       </c>
       <c r="B18" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,48 +2629,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129438622</v>
+        <v>129432686</v>
       </c>
       <c r="B20" t="n">
-        <v>91514</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469988</v>
+        <v>469936</v>
       </c>
       <c r="R20" t="n">
-        <v>7023785</v>
+        <v>7023512</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2699,7 +2708,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2709,7 +2718,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2736,45 +2745,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129433226</v>
+        <v>129438563</v>
       </c>
       <c r="B21" t="n">
-        <v>91323</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3215</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>470038</v>
+        <v>469981</v>
       </c>
       <c r="R21" t="n">
-        <v>7023552</v>
+        <v>7023772</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2806,7 +2824,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2834,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,54 +2861,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129432686</v>
+        <v>129433226</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>91326</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>3215</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469936</v>
+        <v>470038</v>
       </c>
       <c r="R22" t="n">
-        <v>7023512</v>
+        <v>7023552</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2922,7 +2931,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2932,7 +2941,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2959,57 +2968,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129438563</v>
+        <v>129438622</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>91517</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469981</v>
+        <v>469988</v>
       </c>
       <c r="R23" t="n">
-        <v>7023772</v>
+        <v>7023785</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>129438355</v>
       </c>
       <c r="B24" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3307,10 +3307,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129432713</v>
+        <v>129431892</v>
       </c>
       <c r="B26" t="n">
-        <v>97595</v>
+        <v>91517</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3318,43 +3318,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>469891</v>
+        <v>469888</v>
       </c>
       <c r="R26" t="n">
-        <v>7023526</v>
+        <v>7023489</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3386,7 +3377,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3396,12 +3387,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Mkt rikligt</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3428,10 +3414,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129431892</v>
+        <v>129432713</v>
       </c>
       <c r="B27" t="n">
-        <v>91514</v>
+        <v>97598</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3439,34 +3425,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469888</v>
+        <v>469891</v>
       </c>
       <c r="R27" t="n">
-        <v>7023489</v>
+        <v>7023526</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3498,7 +3493,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3508,7 +3503,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Mkt rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3538,7 +3538,7 @@
         <v>129438822</v>
       </c>
       <c r="B28" t="n">
-        <v>92505</v>
+        <v>92508</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>129439057</v>
       </c>
       <c r="B29" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129431802</v>
+        <v>129432249</v>
       </c>
       <c r="B30" t="n">
-        <v>57568</v>
+        <v>92508</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,46 +3756,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102621</v>
+        <v>4769</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469884</v>
+        <v>469890</v>
       </c>
       <c r="R30" t="n">
-        <v>7023463</v>
+        <v>7023461</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3824,7 +3815,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3834,12 +3825,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:26</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Höstläte.</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3866,32 +3852,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129432249</v>
+        <v>129432736</v>
       </c>
       <c r="B31" t="n">
-        <v>92505</v>
+        <v>91553</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3901,13 +3887,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469890</v>
+        <v>469874</v>
       </c>
       <c r="R31" t="n">
-        <v>7023461</v>
+        <v>7023510</v>
       </c>
       <c r="S31" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3936,7 +3922,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3946,7 +3932,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3973,45 +3959,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129432736</v>
+        <v>129431802</v>
       </c>
       <c r="B32" t="n">
-        <v>91550</v>
+        <v>57568</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>102621</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>469874</v>
+        <v>469884</v>
       </c>
       <c r="R32" t="n">
-        <v>7023510</v>
+        <v>7023463</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4043,7 +4038,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4053,7 +4048,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Höstläte.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4080,54 +4080,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129436692</v>
+        <v>129437246</v>
       </c>
       <c r="B33" t="n">
-        <v>91546</v>
+        <v>92508</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>470084</v>
+        <v>470062</v>
       </c>
       <c r="R33" t="n">
-        <v>7023711</v>
+        <v>7023744</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4159,7 +4150,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4169,7 +4160,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4196,45 +4187,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129437246</v>
+        <v>129436692</v>
       </c>
       <c r="B34" t="n">
-        <v>92505</v>
+        <v>91549</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>470062</v>
+        <v>470084</v>
       </c>
       <c r="R34" t="n">
-        <v>7023744</v>
+        <v>7023711</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4530,7 +4530,7 @@
         <v>129433427</v>
       </c>
       <c r="B37" t="n">
-        <v>98641</v>
+        <v>98644</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>129438312</v>
       </c>
       <c r="B38" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4988,10 +4988,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129433079</v>
+        <v>129431850</v>
       </c>
       <c r="B41" t="n">
-        <v>78447</v>
+        <v>57887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4999,37 +4999,51 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>469974</v>
+        <v>469888</v>
       </c>
       <c r="R41" t="n">
-        <v>7023561</v>
+        <v>7023489</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5058,7 +5072,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5068,7 +5082,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5212,10 +5226,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129431850</v>
+        <v>129433079</v>
       </c>
       <c r="B43" t="n">
-        <v>57887</v>
+        <v>78447</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5223,51 +5237,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>469888</v>
+        <v>469974</v>
       </c>
       <c r="R43" t="n">
-        <v>7023489</v>
+        <v>7023561</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5336,7 +5336,7 @@
         <v>129433203</v>
       </c>
       <c r="B44" t="n">
-        <v>105775</v>
+        <v>105778</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v>129438495</v>
       </c>
       <c r="B46" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>129432587</v>
       </c>
       <c r="B47" t="n">
-        <v>98628</v>
+        <v>98631</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>129438794</v>
       </c>
       <c r="B49" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>129432731</v>
       </c>
       <c r="B50" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -1852,32 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129433719</v>
+        <v>129438295</v>
       </c>
       <c r="B13" t="n">
-        <v>78447</v>
+        <v>91517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470105</v>
+        <v>470035</v>
       </c>
       <c r="R13" t="n">
-        <v>7023529</v>
+        <v>7023758</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,32 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129438295</v>
+        <v>129433719</v>
       </c>
       <c r="B14" t="n">
-        <v>91517</v>
+        <v>78447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470035</v>
+        <v>470105</v>
       </c>
       <c r="R14" t="n">
-        <v>7023758</v>
+        <v>7023529</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2629,54 +2629,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129432686</v>
+        <v>129433226</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>91326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>3215</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469936</v>
+        <v>470038</v>
       </c>
       <c r="R20" t="n">
-        <v>7023512</v>
+        <v>7023552</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2708,7 +2699,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2718,7 +2709,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2745,57 +2736,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129438563</v>
+        <v>129438622</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>91517</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469981</v>
+        <v>469988</v>
       </c>
       <c r="R21" t="n">
-        <v>7023772</v>
+        <v>7023785</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2861,45 +2843,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129433226</v>
+        <v>129432686</v>
       </c>
       <c r="B22" t="n">
-        <v>91326</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3215</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>470038</v>
+        <v>469936</v>
       </c>
       <c r="R22" t="n">
-        <v>7023552</v>
+        <v>7023512</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2931,7 +2922,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2941,7 +2932,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2968,48 +2959,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129438622</v>
+        <v>129438563</v>
       </c>
       <c r="B23" t="n">
-        <v>91517</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469988</v>
+        <v>469981</v>
       </c>
       <c r="R23" t="n">
-        <v>7023785</v>
+        <v>7023772</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3191,42 +3191,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129438443</v>
+        <v>129432713</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>97598</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>469996</v>
+        <v>469891</v>
       </c>
       <c r="R25" t="n">
-        <v>7023753</v>
+        <v>7023526</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3280,7 +3280,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Mkt rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3414,42 +3419,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129432713</v>
+        <v>129438443</v>
       </c>
       <c r="B27" t="n">
-        <v>97598</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3458,10 +3463,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469891</v>
+        <v>469996</v>
       </c>
       <c r="R27" t="n">
-        <v>7023526</v>
+        <v>7023753</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3493,7 +3498,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3503,12 +3508,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Mkt rikligt</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3745,32 +3745,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129432249</v>
+        <v>129432736</v>
       </c>
       <c r="B30" t="n">
-        <v>92508</v>
+        <v>91553</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3780,13 +3780,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469890</v>
+        <v>469874</v>
       </c>
       <c r="R30" t="n">
-        <v>7023461</v>
+        <v>7023510</v>
       </c>
       <c r="S30" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3852,45 +3852,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129432736</v>
+        <v>129431802</v>
       </c>
       <c r="B31" t="n">
-        <v>91553</v>
+        <v>57568</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>102621</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469874</v>
+        <v>469884</v>
       </c>
       <c r="R31" t="n">
-        <v>7023510</v>
+        <v>7023463</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3922,7 +3931,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3932,7 +3941,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Höstläte.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3959,10 +3973,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129431802</v>
+        <v>129432249</v>
       </c>
       <c r="B32" t="n">
-        <v>57568</v>
+        <v>92508</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3970,46 +3984,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102621</v>
+        <v>4769</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>469884</v>
+        <v>469890</v>
       </c>
       <c r="R32" t="n">
-        <v>7023463</v>
+        <v>7023461</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4038,7 +4043,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4048,12 +4053,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:26</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Höstläte.</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4303,10 +4303,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129432551</v>
+        <v>129435273</v>
       </c>
       <c r="B35" t="n">
-        <v>83004</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4314,34 +4314,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>469918</v>
+        <v>470105</v>
       </c>
       <c r="R35" t="n">
-        <v>7023461</v>
+        <v>7023529</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4373,7 +4378,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4383,12 +4388,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På björkstubbe.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4415,10 +4415,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129435273</v>
+        <v>129432551</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>83004</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4426,39 +4426,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>470105</v>
+        <v>469918</v>
       </c>
       <c r="R36" t="n">
-        <v>7023529</v>
+        <v>7023461</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4490,7 +4485,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4500,7 +4495,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På björkstubbe.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4988,10 +4988,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129431850</v>
+        <v>129433079</v>
       </c>
       <c r="B41" t="n">
-        <v>57887</v>
+        <v>78447</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4999,51 +4999,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>469888</v>
+        <v>469974</v>
       </c>
       <c r="R41" t="n">
-        <v>7023489</v>
+        <v>7023561</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5072,7 +5058,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5082,7 +5068,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5226,10 +5212,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129433079</v>
+        <v>129431850</v>
       </c>
       <c r="B43" t="n">
-        <v>78447</v>
+        <v>57887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5237,37 +5223,51 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>469974</v>
+        <v>469888</v>
       </c>
       <c r="R43" t="n">
-        <v>7023561</v>
+        <v>7023489</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -1852,32 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129438295</v>
+        <v>129433719</v>
       </c>
       <c r="B13" t="n">
-        <v>91517</v>
+        <v>78447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470035</v>
+        <v>470105</v>
       </c>
       <c r="R13" t="n">
-        <v>7023758</v>
+        <v>7023529</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,32 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129433719</v>
+        <v>129438295</v>
       </c>
       <c r="B14" t="n">
-        <v>78447</v>
+        <v>91517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470105</v>
+        <v>470035</v>
       </c>
       <c r="R14" t="n">
-        <v>7023529</v>
+        <v>7023758</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2736,45 +2736,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129438622</v>
+        <v>129438355</v>
       </c>
       <c r="B21" t="n">
-        <v>91517</v>
+        <v>98727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469988</v>
+        <v>470019</v>
       </c>
       <c r="R21" t="n">
-        <v>7023785</v>
+        <v>7023756</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2806,7 +2815,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2825,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3075,54 +3084,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129438355</v>
+        <v>129438622</v>
       </c>
       <c r="B24" t="n">
-        <v>98727</v>
+        <v>91517</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>470019</v>
+        <v>469988</v>
       </c>
       <c r="R24" t="n">
-        <v>7023756</v>
+        <v>7023785</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3191,10 +3191,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129432713</v>
+        <v>129431892</v>
       </c>
       <c r="B25" t="n">
-        <v>97598</v>
+        <v>91517</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3202,43 +3202,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>469891</v>
+        <v>469888</v>
       </c>
       <c r="R25" t="n">
-        <v>7023526</v>
+        <v>7023489</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3270,7 +3261,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3280,12 +3271,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Mkt rikligt</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3312,45 +3298,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129431892</v>
+        <v>129438443</v>
       </c>
       <c r="B26" t="n">
-        <v>91517</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>469888</v>
+        <v>469996</v>
       </c>
       <c r="R26" t="n">
-        <v>7023489</v>
+        <v>7023753</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3382,7 +3377,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3392,7 +3387,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3419,42 +3414,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129438443</v>
+        <v>129432713</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>97598</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3463,10 +3458,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469996</v>
+        <v>469891</v>
       </c>
       <c r="R27" t="n">
-        <v>7023753</v>
+        <v>7023526</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3498,7 +3493,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3508,7 +3503,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Mkt rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3642,10 +3642,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129439057</v>
+        <v>129432736</v>
       </c>
       <c r="B29" t="n">
-        <v>91573</v>
+        <v>91553</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3653,19 +3653,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3673,10 +3677,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>470060</v>
+        <v>469874</v>
       </c>
       <c r="R29" t="n">
-        <v>7023719</v>
+        <v>7023510</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3708,7 +3712,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3718,7 +3722,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3745,10 +3749,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129432736</v>
+        <v>129439057</v>
       </c>
       <c r="B30" t="n">
-        <v>91553</v>
+        <v>91573</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,23 +3760,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469874</v>
+        <v>470060</v>
       </c>
       <c r="R30" t="n">
-        <v>7023510</v>
+        <v>7023719</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3852,10 +3852,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129431802</v>
+        <v>129432249</v>
       </c>
       <c r="B31" t="n">
-        <v>57568</v>
+        <v>92508</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3863,46 +3863,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102621</v>
+        <v>4769</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469884</v>
+        <v>469890</v>
       </c>
       <c r="R31" t="n">
-        <v>7023463</v>
+        <v>7023461</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3931,7 +3922,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3941,12 +3932,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:26</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Höstläte.</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3973,10 +3959,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129432249</v>
+        <v>129431802</v>
       </c>
       <c r="B32" t="n">
-        <v>92508</v>
+        <v>57568</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3984,37 +3970,46 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4769</v>
+        <v>102621</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>469890</v>
+        <v>469884</v>
       </c>
       <c r="R32" t="n">
-        <v>7023461</v>
+        <v>7023463</v>
       </c>
       <c r="S32" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4043,7 +4038,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4053,7 +4048,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Höstläte.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4303,10 +4303,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129435273</v>
+        <v>129432551</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>83004</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4314,39 +4314,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>470105</v>
+        <v>469918</v>
       </c>
       <c r="R35" t="n">
-        <v>7023529</v>
+        <v>7023461</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4378,7 +4373,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4388,7 +4383,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På björkstubbe.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4415,10 +4415,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129432551</v>
+        <v>129435273</v>
       </c>
       <c r="B36" t="n">
-        <v>83004</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4426,34 +4426,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>469918</v>
+        <v>470105</v>
       </c>
       <c r="R36" t="n">
-        <v>7023461</v>
+        <v>7023529</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4485,7 +4490,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4495,12 +4500,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På björkstubbe.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4759,7 +4759,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129433664</v>
+        <v>129437140</v>
       </c>
       <c r="B39" t="n">
         <v>57724</v>
@@ -4799,13 +4799,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>470092</v>
+        <v>470060</v>
       </c>
       <c r="R39" t="n">
-        <v>7023517</v>
+        <v>7023746</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4844,12 +4844,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Bearbetad torraka.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4876,7 +4871,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129437140</v>
+        <v>129433664</v>
       </c>
       <c r="B40" t="n">
         <v>57724</v>
@@ -4916,13 +4911,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>470060</v>
+        <v>470092</v>
       </c>
       <c r="R40" t="n">
-        <v>7023746</v>
+        <v>7023517</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4951,7 +4946,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4961,7 +4956,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Bearbetad torraka.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5570,45 +5570,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129438495</v>
+        <v>129432587</v>
       </c>
       <c r="B46" t="n">
-        <v>91553</v>
+        <v>98631</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>220093</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>470000</v>
+        <v>469915</v>
       </c>
       <c r="R46" t="n">
-        <v>7023770</v>
+        <v>7023493</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5640,7 +5649,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5650,7 +5659,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5677,54 +5686,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129432587</v>
+        <v>129438495</v>
       </c>
       <c r="B47" t="n">
-        <v>98631</v>
+        <v>91553</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220093</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>469915</v>
+        <v>470000</v>
       </c>
       <c r="R47" t="n">
-        <v>7023493</v>
+        <v>7023770</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5793,10 +5793,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129437030</v>
+        <v>129438794</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5804,21 +5804,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>470069</v>
+        <v>469986</v>
       </c>
       <c r="R48" t="n">
-        <v>7023735</v>
+        <v>7023830</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5900,10 +5900,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129438794</v>
+        <v>129437030</v>
       </c>
       <c r="B49" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5911,21 +5911,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>469986</v>
+        <v>470069</v>
       </c>
       <c r="R49" t="n">
-        <v>7023830</v>
+        <v>7023735</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -1852,32 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129433719</v>
+        <v>129438295</v>
       </c>
       <c r="B13" t="n">
-        <v>78447</v>
+        <v>91517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470105</v>
+        <v>470035</v>
       </c>
       <c r="R13" t="n">
-        <v>7023529</v>
+        <v>7023758</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,32 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129438295</v>
+        <v>129433719</v>
       </c>
       <c r="B14" t="n">
-        <v>91517</v>
+        <v>78447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470035</v>
+        <v>470105</v>
       </c>
       <c r="R14" t="n">
-        <v>7023758</v>
+        <v>7023529</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,45 +2173,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129438250</v>
+        <v>129438342</v>
       </c>
       <c r="B16" t="n">
-        <v>91326</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470035</v>
+        <v>470019</v>
       </c>
       <c r="R16" t="n">
-        <v>7023758</v>
+        <v>7023755</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2252,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2262,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,50 +2289,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129436901</v>
+        <v>129438250</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>91326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470084</v>
+        <v>470035</v>
       </c>
       <c r="R17" t="n">
-        <v>7023711</v>
+        <v>7023758</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2359,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2365,12 +2369,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Barkflag på gran</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2397,42 +2396,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129438342</v>
+        <v>129436901</v>
       </c>
       <c r="B18" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2441,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>470019</v>
+        <v>470084</v>
       </c>
       <c r="R18" t="n">
-        <v>7023755</v>
+        <v>7023711</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2476,7 +2471,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2486,7 +2481,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Barkflag på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2736,54 +2736,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129438355</v>
+        <v>129438622</v>
       </c>
       <c r="B21" t="n">
-        <v>98727</v>
+        <v>91517</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>470019</v>
+        <v>469988</v>
       </c>
       <c r="R21" t="n">
-        <v>7023756</v>
+        <v>7023785</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2815,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2825,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3084,45 +3075,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129438622</v>
+        <v>129438355</v>
       </c>
       <c r="B24" t="n">
-        <v>91517</v>
+        <v>98727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>469988</v>
+        <v>470019</v>
       </c>
       <c r="R24" t="n">
-        <v>7023785</v>
+        <v>7023756</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3191,45 +3191,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129431892</v>
+        <v>129438443</v>
       </c>
       <c r="B25" t="n">
-        <v>91517</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>469888</v>
+        <v>469996</v>
       </c>
       <c r="R25" t="n">
-        <v>7023489</v>
+        <v>7023753</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3261,7 +3270,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3271,7 +3280,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3298,54 +3307,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129438443</v>
+        <v>129431892</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>91517</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>469996</v>
+        <v>469888</v>
       </c>
       <c r="R26" t="n">
-        <v>7023753</v>
+        <v>7023489</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3377,7 +3377,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3642,32 +3642,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129432736</v>
+        <v>129432249</v>
       </c>
       <c r="B29" t="n">
-        <v>91553</v>
+        <v>92508</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3677,13 +3677,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469874</v>
+        <v>469890</v>
       </c>
       <c r="R29" t="n">
-        <v>7023510</v>
+        <v>7023461</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3852,32 +3852,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129432249</v>
+        <v>129432736</v>
       </c>
       <c r="B31" t="n">
-        <v>92508</v>
+        <v>91553</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469890</v>
+        <v>469874</v>
       </c>
       <c r="R31" t="n">
-        <v>7023461</v>
+        <v>7023510</v>
       </c>
       <c r="S31" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4080,45 +4080,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129437246</v>
+        <v>129436692</v>
       </c>
       <c r="B33" t="n">
-        <v>92508</v>
+        <v>91549</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>470062</v>
+        <v>470084</v>
       </c>
       <c r="R33" t="n">
-        <v>7023744</v>
+        <v>7023711</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4150,7 +4159,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4160,7 +4169,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4187,54 +4196,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129436692</v>
+        <v>129437246</v>
       </c>
       <c r="B34" t="n">
-        <v>91549</v>
+        <v>92508</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>470084</v>
+        <v>470062</v>
       </c>
       <c r="R34" t="n">
-        <v>7023711</v>
+        <v>7023744</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4759,7 +4759,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129437140</v>
+        <v>129433664</v>
       </c>
       <c r="B39" t="n">
         <v>57724</v>
@@ -4799,13 +4799,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>470060</v>
+        <v>470092</v>
       </c>
       <c r="R39" t="n">
-        <v>7023746</v>
+        <v>7023517</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4844,7 +4844,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Bearbetad torraka.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4871,7 +4876,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129433664</v>
+        <v>129437140</v>
       </c>
       <c r="B40" t="n">
         <v>57724</v>
@@ -4911,13 +4916,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>470092</v>
+        <v>470060</v>
       </c>
       <c r="R40" t="n">
-        <v>7023517</v>
+        <v>7023746</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4946,7 +4951,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4956,12 +4961,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Bearbetad torraka.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4988,10 +4988,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129433079</v>
+        <v>129431850</v>
       </c>
       <c r="B41" t="n">
-        <v>78447</v>
+        <v>57887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4999,37 +4999,51 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>469974</v>
+        <v>469888</v>
       </c>
       <c r="R41" t="n">
-        <v>7023561</v>
+        <v>7023489</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5058,7 +5072,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5068,7 +5082,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5095,10 +5109,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129438474</v>
+        <v>129433079</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>78447</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5106,42 +5120,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469996</v>
+        <v>469974</v>
       </c>
       <c r="R42" t="n">
-        <v>7023753</v>
+        <v>7023561</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5170,7 +5179,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5180,12 +5189,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Barkflag/ringhack</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5212,10 +5216,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129431850</v>
+        <v>129438474</v>
       </c>
       <c r="B43" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5223,36 +5227,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5261,10 +5256,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>469888</v>
+        <v>469996</v>
       </c>
       <c r="R43" t="n">
-        <v>7023489</v>
+        <v>7023753</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5296,7 +5291,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5306,7 +5301,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Barkflag/ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -1852,32 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129438295</v>
+        <v>129433719</v>
       </c>
       <c r="B13" t="n">
-        <v>91517</v>
+        <v>78447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470035</v>
+        <v>470105</v>
       </c>
       <c r="R13" t="n">
-        <v>7023758</v>
+        <v>7023529</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,32 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129433719</v>
+        <v>129438295</v>
       </c>
       <c r="B14" t="n">
-        <v>78447</v>
+        <v>91517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470105</v>
+        <v>470035</v>
       </c>
       <c r="R14" t="n">
-        <v>7023529</v>
+        <v>7023758</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,42 +2173,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129438342</v>
+        <v>129436901</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2217,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470019</v>
+        <v>470084</v>
       </c>
       <c r="R16" t="n">
-        <v>7023755</v>
+        <v>7023711</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2262,7 +2258,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Barkflag på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,38 +2397,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129436901</v>
+        <v>129438342</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2436,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>470084</v>
+        <v>470019</v>
       </c>
       <c r="R18" t="n">
-        <v>7023711</v>
+        <v>7023755</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2471,7 +2476,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2481,12 +2486,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Barkflag på gran</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2736,45 +2736,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129438622</v>
+        <v>129438355</v>
       </c>
       <c r="B21" t="n">
-        <v>91517</v>
+        <v>98727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469988</v>
+        <v>470019</v>
       </c>
       <c r="R21" t="n">
-        <v>7023785</v>
+        <v>7023756</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2806,7 +2815,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2825,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,7 +2852,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129432686</v>
+        <v>129438563</v>
       </c>
       <c r="B22" t="n">
         <v>57887</v>
@@ -2873,7 +2882,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2887,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469936</v>
+        <v>469981</v>
       </c>
       <c r="R22" t="n">
-        <v>7023512</v>
+        <v>7023772</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2922,7 +2931,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2932,7 +2941,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2959,7 +2968,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129438563</v>
+        <v>129432686</v>
       </c>
       <c r="B23" t="n">
         <v>57887</v>
@@ -2989,7 +2998,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3003,10 +3012,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469981</v>
+        <v>469936</v>
       </c>
       <c r="R23" t="n">
-        <v>7023772</v>
+        <v>7023512</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3038,7 +3047,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3048,7 +3057,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3075,54 +3084,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129438355</v>
+        <v>129438622</v>
       </c>
       <c r="B24" t="n">
-        <v>98727</v>
+        <v>91517</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>470019</v>
+        <v>469988</v>
       </c>
       <c r="R24" t="n">
-        <v>7023756</v>
+        <v>7023785</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3191,54 +3191,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129438443</v>
+        <v>129431892</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>91517</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>469996</v>
+        <v>469888</v>
       </c>
       <c r="R25" t="n">
-        <v>7023753</v>
+        <v>7023489</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3270,7 +3261,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3280,7 +3271,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3307,45 +3298,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129431892</v>
+        <v>129438443</v>
       </c>
       <c r="B26" t="n">
-        <v>91517</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>469888</v>
+        <v>469996</v>
       </c>
       <c r="R26" t="n">
-        <v>7023489</v>
+        <v>7023753</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3377,7 +3377,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3642,32 +3642,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129432249</v>
+        <v>129432736</v>
       </c>
       <c r="B29" t="n">
-        <v>92508</v>
+        <v>91553</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3677,13 +3677,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469890</v>
+        <v>469874</v>
       </c>
       <c r="R29" t="n">
-        <v>7023461</v>
+        <v>7023510</v>
       </c>
       <c r="S29" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3852,32 +3852,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129432736</v>
+        <v>129432249</v>
       </c>
       <c r="B31" t="n">
-        <v>91553</v>
+        <v>92508</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469874</v>
+        <v>469890</v>
       </c>
       <c r="R31" t="n">
-        <v>7023510</v>
+        <v>7023461</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4080,54 +4080,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129436692</v>
+        <v>129437246</v>
       </c>
       <c r="B33" t="n">
-        <v>91549</v>
+        <v>92508</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>470084</v>
+        <v>470062</v>
       </c>
       <c r="R33" t="n">
-        <v>7023711</v>
+        <v>7023744</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4159,7 +4150,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4169,7 +4160,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4196,45 +4187,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129437246</v>
+        <v>129436692</v>
       </c>
       <c r="B34" t="n">
-        <v>92508</v>
+        <v>91549</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>470062</v>
+        <v>470084</v>
       </c>
       <c r="R34" t="n">
-        <v>7023744</v>
+        <v>7023711</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4759,7 +4759,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129433664</v>
+        <v>129437140</v>
       </c>
       <c r="B39" t="n">
         <v>57724</v>
@@ -4799,13 +4799,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>470092</v>
+        <v>470060</v>
       </c>
       <c r="R39" t="n">
-        <v>7023517</v>
+        <v>7023746</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4844,12 +4844,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Bearbetad torraka.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4876,7 +4871,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129437140</v>
+        <v>129433664</v>
       </c>
       <c r="B40" t="n">
         <v>57724</v>
@@ -4916,13 +4911,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>470060</v>
+        <v>470092</v>
       </c>
       <c r="R40" t="n">
-        <v>7023746</v>
+        <v>7023517</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4951,7 +4946,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4961,7 +4956,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Bearbetad torraka.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4988,10 +4988,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129431850</v>
+        <v>129433079</v>
       </c>
       <c r="B41" t="n">
-        <v>57887</v>
+        <v>78447</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4999,51 +4999,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>469888</v>
+        <v>469974</v>
       </c>
       <c r="R41" t="n">
-        <v>7023489</v>
+        <v>7023561</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5072,7 +5058,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5082,7 +5068,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5109,10 +5095,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129433079</v>
+        <v>129438474</v>
       </c>
       <c r="B42" t="n">
-        <v>78447</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5120,37 +5106,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469974</v>
+        <v>469996</v>
       </c>
       <c r="R42" t="n">
-        <v>7023561</v>
+        <v>7023753</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5179,7 +5170,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5189,7 +5180,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Barkflag/ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5216,10 +5212,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129438474</v>
+        <v>129431850</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5227,27 +5223,36 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5256,10 +5261,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>469996</v>
+        <v>469888</v>
       </c>
       <c r="R43" t="n">
-        <v>7023753</v>
+        <v>7023489</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5291,7 +5296,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5301,12 +5306,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Barkflag/ringhack</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5570,54 +5570,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129432587</v>
+        <v>129438495</v>
       </c>
       <c r="B46" t="n">
-        <v>98631</v>
+        <v>91553</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220093</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>469915</v>
+        <v>470000</v>
       </c>
       <c r="R46" t="n">
-        <v>7023493</v>
+        <v>7023770</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5649,7 +5640,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5659,7 +5650,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5686,45 +5677,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129438495</v>
+        <v>129432587</v>
       </c>
       <c r="B47" t="n">
-        <v>91553</v>
+        <v>98631</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>220093</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>470000</v>
+        <v>469915</v>
       </c>
       <c r="R47" t="n">
-        <v>7023770</v>
+        <v>7023493</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5793,10 +5793,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129438794</v>
+        <v>129437030</v>
       </c>
       <c r="B48" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5804,21 +5804,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>469986</v>
+        <v>470069</v>
       </c>
       <c r="R48" t="n">
-        <v>7023830</v>
+        <v>7023735</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5900,10 +5900,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129437030</v>
+        <v>129438794</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5911,21 +5911,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>470069</v>
+        <v>469986</v>
       </c>
       <c r="R49" t="n">
-        <v>7023735</v>
+        <v>7023830</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -2173,50 +2173,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129436901</v>
+        <v>129438250</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>91326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470084</v>
+        <v>470035</v>
       </c>
       <c r="R16" t="n">
-        <v>7023711</v>
+        <v>7023758</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2258,12 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Barkflag på gran</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2290,45 +2280,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129438250</v>
+        <v>129436901</v>
       </c>
       <c r="B17" t="n">
-        <v>91326</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3215</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470035</v>
+        <v>470084</v>
       </c>
       <c r="R17" t="n">
-        <v>7023758</v>
+        <v>7023711</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2370,7 +2365,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Barkflag på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2629,10 +2629,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129433226</v>
+        <v>129438622</v>
       </c>
       <c r="B20" t="n">
-        <v>91326</v>
+        <v>91517</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2640,21 +2640,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3215</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2664,13 +2664,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>470038</v>
+        <v>469988</v>
       </c>
       <c r="R20" t="n">
-        <v>7023552</v>
+        <v>7023785</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2852,54 +2852,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129438563</v>
+        <v>129433226</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>91326</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>3215</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469981</v>
+        <v>470038</v>
       </c>
       <c r="R22" t="n">
-        <v>7023772</v>
+        <v>7023552</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2931,7 +2922,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2941,7 +2932,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3084,48 +3075,57 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129438622</v>
+        <v>129438563</v>
       </c>
       <c r="B24" t="n">
-        <v>91517</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>469988</v>
+        <v>469981</v>
       </c>
       <c r="R24" t="n">
-        <v>7023785</v>
+        <v>7023772</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3191,45 +3191,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129431892</v>
+        <v>129438443</v>
       </c>
       <c r="B25" t="n">
-        <v>91517</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>469888</v>
+        <v>469996</v>
       </c>
       <c r="R25" t="n">
-        <v>7023489</v>
+        <v>7023753</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3261,7 +3270,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3271,7 +3280,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3298,42 +3307,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129438443</v>
+        <v>129432713</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>97598</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3342,10 +3351,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>469996</v>
+        <v>469891</v>
       </c>
       <c r="R26" t="n">
-        <v>7023753</v>
+        <v>7023526</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3377,7 +3386,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3387,7 +3396,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Mkt rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3414,10 +3428,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129432713</v>
+        <v>129431892</v>
       </c>
       <c r="B27" t="n">
-        <v>97598</v>
+        <v>91517</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3425,43 +3439,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469891</v>
+        <v>469888</v>
       </c>
       <c r="R27" t="n">
-        <v>7023526</v>
+        <v>7023489</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3493,7 +3498,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3503,12 +3508,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Mkt rikligt</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3749,30 +3749,34 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129439057</v>
+        <v>129432249</v>
       </c>
       <c r="B30" t="n">
-        <v>91573</v>
+        <v>92508</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3780,13 +3784,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>470060</v>
+        <v>469890</v>
       </c>
       <c r="R30" t="n">
-        <v>7023719</v>
+        <v>7023461</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3815,7 +3819,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3825,7 +3829,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3852,34 +3856,30 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129432249</v>
+        <v>129439057</v>
       </c>
       <c r="B31" t="n">
-        <v>92508</v>
+        <v>91573</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469890</v>
+        <v>470060</v>
       </c>
       <c r="R31" t="n">
-        <v>7023461</v>
+        <v>7023719</v>
       </c>
       <c r="S31" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4080,45 +4080,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129437246</v>
+        <v>129436692</v>
       </c>
       <c r="B33" t="n">
-        <v>92508</v>
+        <v>91549</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>470062</v>
+        <v>470084</v>
       </c>
       <c r="R33" t="n">
-        <v>7023744</v>
+        <v>7023711</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4150,7 +4159,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4160,7 +4169,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4187,54 +4196,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129436692</v>
+        <v>129437246</v>
       </c>
       <c r="B34" t="n">
-        <v>91549</v>
+        <v>92508</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>470084</v>
+        <v>470062</v>
       </c>
       <c r="R34" t="n">
-        <v>7023711</v>
+        <v>7023744</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4759,7 +4759,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129437140</v>
+        <v>129433664</v>
       </c>
       <c r="B39" t="n">
         <v>57724</v>
@@ -4799,13 +4799,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>470060</v>
+        <v>470092</v>
       </c>
       <c r="R39" t="n">
-        <v>7023746</v>
+        <v>7023517</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4844,7 +4844,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Bearbetad torraka.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4871,7 +4876,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129433664</v>
+        <v>129437140</v>
       </c>
       <c r="B40" t="n">
         <v>57724</v>
@@ -4911,13 +4916,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>470092</v>
+        <v>470060</v>
       </c>
       <c r="R40" t="n">
-        <v>7023517</v>
+        <v>7023746</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4946,7 +4951,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4956,12 +4961,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Bearbetad torraka.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5570,45 +5570,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129438495</v>
+        <v>129432587</v>
       </c>
       <c r="B46" t="n">
-        <v>91553</v>
+        <v>98631</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>220093</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>470000</v>
+        <v>469915</v>
       </c>
       <c r="R46" t="n">
-        <v>7023770</v>
+        <v>7023493</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5640,7 +5649,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5650,7 +5659,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5677,54 +5686,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129432587</v>
+        <v>129438495</v>
       </c>
       <c r="B47" t="n">
-        <v>98631</v>
+        <v>91553</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220093</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>469915</v>
+        <v>470000</v>
       </c>
       <c r="R47" t="n">
-        <v>7023493</v>
+        <v>7023770</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5793,10 +5793,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129437030</v>
+        <v>129438794</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5804,21 +5804,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>470069</v>
+        <v>469986</v>
       </c>
       <c r="R48" t="n">
-        <v>7023735</v>
+        <v>7023830</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5900,10 +5900,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129438794</v>
+        <v>129437030</v>
       </c>
       <c r="B49" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5911,21 +5911,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>469986</v>
+        <v>470069</v>
       </c>
       <c r="R49" t="n">
-        <v>7023830</v>
+        <v>7023735</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -1852,32 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129433719</v>
+        <v>129438295</v>
       </c>
       <c r="B13" t="n">
-        <v>78447</v>
+        <v>91545</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470105</v>
+        <v>470035</v>
       </c>
       <c r="R13" t="n">
-        <v>7023529</v>
+        <v>7023758</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,32 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129438295</v>
+        <v>129433719</v>
       </c>
       <c r="B14" t="n">
-        <v>91517</v>
+        <v>78473</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470035</v>
+        <v>470105</v>
       </c>
       <c r="R14" t="n">
-        <v>7023758</v>
+        <v>7023529</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,7 +2069,7 @@
         <v>129436988</v>
       </c>
       <c r="B15" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>129438250</v>
       </c>
       <c r="B16" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>129436901</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>129438342</v>
       </c>
       <c r="B18" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>129433401</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129438622</v>
+        <v>129433226</v>
       </c>
       <c r="B20" t="n">
-        <v>91517</v>
+        <v>91354</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2640,21 +2640,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>3215</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2664,13 +2664,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469988</v>
+        <v>470038</v>
       </c>
       <c r="R20" t="n">
-        <v>7023785</v>
+        <v>7023552</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2736,54 +2736,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129438355</v>
+        <v>129438622</v>
       </c>
       <c r="B21" t="n">
-        <v>98727</v>
+        <v>91545</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>470019</v>
+        <v>469988</v>
       </c>
       <c r="R21" t="n">
-        <v>7023756</v>
+        <v>7023785</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2815,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2825,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2852,48 +2843,57 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129433226</v>
+        <v>129438355</v>
       </c>
       <c r="B22" t="n">
-        <v>91326</v>
+        <v>98756</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>470038</v>
+        <v>470019</v>
       </c>
       <c r="R22" t="n">
-        <v>7023552</v>
+        <v>7023756</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2962,7 +2962,7 @@
         <v>129432686</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>129438563</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3191,54 +3191,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129438443</v>
+        <v>129431892</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>91545</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>469996</v>
+        <v>469888</v>
       </c>
       <c r="R25" t="n">
-        <v>7023753</v>
+        <v>7023489</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3270,7 +3261,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3280,7 +3271,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3307,42 +3298,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129432713</v>
+        <v>129438443</v>
       </c>
       <c r="B26" t="n">
-        <v>97598</v>
+        <v>57890</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3351,10 +3342,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>469891</v>
+        <v>469996</v>
       </c>
       <c r="R26" t="n">
-        <v>7023526</v>
+        <v>7023753</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3386,7 +3377,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3396,12 +3387,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Mkt rikligt</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3428,10 +3414,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129431892</v>
+        <v>129432713</v>
       </c>
       <c r="B27" t="n">
-        <v>91517</v>
+        <v>97627</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3439,34 +3425,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469888</v>
+        <v>469891</v>
       </c>
       <c r="R27" t="n">
-        <v>7023489</v>
+        <v>7023526</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3498,7 +3493,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3508,7 +3503,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Mkt rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3538,7 +3538,7 @@
         <v>129438822</v>
       </c>
       <c r="B28" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3642,32 +3642,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129432736</v>
+        <v>129432249</v>
       </c>
       <c r="B29" t="n">
-        <v>91553</v>
+        <v>92536</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3677,13 +3677,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469874</v>
+        <v>469890</v>
       </c>
       <c r="R29" t="n">
-        <v>7023510</v>
+        <v>7023461</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3749,10 +3749,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129432249</v>
+        <v>129431802</v>
       </c>
       <c r="B30" t="n">
-        <v>92508</v>
+        <v>57571</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3760,37 +3760,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4769</v>
+        <v>102621</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469890</v>
+        <v>469884</v>
       </c>
       <c r="R30" t="n">
-        <v>7023461</v>
+        <v>7023463</v>
       </c>
       <c r="S30" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3819,7 +3828,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3829,7 +3838,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Höstläte.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3856,10 +3870,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129439057</v>
+        <v>129432736</v>
       </c>
       <c r="B31" t="n">
-        <v>91573</v>
+        <v>91581</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3867,19 +3881,23 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3887,10 +3905,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>470060</v>
+        <v>469874</v>
       </c>
       <c r="R31" t="n">
-        <v>7023719</v>
+        <v>7023510</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3922,7 +3940,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3932,7 +3950,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3959,54 +3977,41 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129431802</v>
+        <v>129439057</v>
       </c>
       <c r="B32" t="n">
-        <v>57568</v>
+        <v>91601</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102621</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>469884</v>
+        <v>470060</v>
       </c>
       <c r="R32" t="n">
-        <v>7023463</v>
+        <v>7023719</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4038,7 +4043,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4048,12 +4053,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:26</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Höstläte.</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4083,7 +4083,7 @@
         <v>129436692</v>
       </c>
       <c r="B33" t="n">
-        <v>91549</v>
+        <v>91577</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>129437246</v>
       </c>
       <c r="B34" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4303,10 +4303,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129432551</v>
+        <v>129435273</v>
       </c>
       <c r="B35" t="n">
-        <v>83004</v>
+        <v>57730</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4314,34 +4314,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>469918</v>
+        <v>470105</v>
       </c>
       <c r="R35" t="n">
-        <v>7023461</v>
+        <v>7023529</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4373,7 +4378,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4383,12 +4388,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På björkstubbe.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4415,10 +4415,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129435273</v>
+        <v>129432551</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>83031</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4426,39 +4426,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>470105</v>
+        <v>469918</v>
       </c>
       <c r="R36" t="n">
-        <v>7023529</v>
+        <v>7023461</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4490,7 +4485,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4500,7 +4495,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På björkstubbe.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4530,7 +4530,7 @@
         <v>129433427</v>
       </c>
       <c r="B37" t="n">
-        <v>98644</v>
+        <v>98673</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>129438312</v>
       </c>
       <c r="B38" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>129433664</v>
       </c>
       <c r="B39" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>129437140</v>
       </c>
       <c r="B40" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>129433079</v>
       </c>
       <c r="B41" t="n">
-        <v>78447</v>
+        <v>78473</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5095,10 +5095,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129438474</v>
+        <v>129431850</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>57890</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5106,27 +5106,36 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5135,10 +5144,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469996</v>
+        <v>469888</v>
       </c>
       <c r="R42" t="n">
-        <v>7023753</v>
+        <v>7023489</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5170,7 +5179,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5180,12 +5189,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Barkflag/ringhack</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5212,10 +5216,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129431850</v>
+        <v>129438474</v>
       </c>
       <c r="B43" t="n">
-        <v>57887</v>
+        <v>57730</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5223,36 +5227,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5261,10 +5256,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>469888</v>
+        <v>469996</v>
       </c>
       <c r="R43" t="n">
-        <v>7023489</v>
+        <v>7023753</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5296,7 +5291,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5306,7 +5301,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Barkflag/ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5336,7 +5336,7 @@
         <v>129433203</v>
       </c>
       <c r="B44" t="n">
-        <v>105778</v>
+        <v>105807</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>129431867</v>
       </c>
       <c r="B45" t="n">
-        <v>58360</v>
+        <v>58363</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5570,54 +5570,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129432587</v>
+        <v>129438495</v>
       </c>
       <c r="B46" t="n">
-        <v>98631</v>
+        <v>91581</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220093</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>469915</v>
+        <v>470000</v>
       </c>
       <c r="R46" t="n">
-        <v>7023493</v>
+        <v>7023770</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5649,7 +5640,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5659,7 +5650,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5686,45 +5677,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129438495</v>
+        <v>129432587</v>
       </c>
       <c r="B47" t="n">
-        <v>91553</v>
+        <v>98660</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>220093</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>470000</v>
+        <v>469915</v>
       </c>
       <c r="R47" t="n">
-        <v>7023770</v>
+        <v>7023493</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5796,7 +5796,7 @@
         <v>129438794</v>
       </c>
       <c r="B48" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>129437030</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>129432731</v>
       </c>
       <c r="B50" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -4988,10 +4988,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129433079</v>
+        <v>129431850</v>
       </c>
       <c r="B41" t="n">
-        <v>78473</v>
+        <v>57890</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4999,37 +4999,51 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>469974</v>
+        <v>469888</v>
       </c>
       <c r="R41" t="n">
-        <v>7023561</v>
+        <v>7023489</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5058,7 +5072,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5068,7 +5082,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5095,10 +5109,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129431850</v>
+        <v>129433079</v>
       </c>
       <c r="B42" t="n">
-        <v>57890</v>
+        <v>78473</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5106,51 +5120,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469888</v>
+        <v>469974</v>
       </c>
       <c r="R42" t="n">
-        <v>7023489</v>
+        <v>7023561</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -1852,32 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129438295</v>
+        <v>129433719</v>
       </c>
       <c r="B13" t="n">
-        <v>91545</v>
+        <v>78478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470035</v>
+        <v>470105</v>
       </c>
       <c r="R13" t="n">
-        <v>7023758</v>
+        <v>7023529</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,32 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129433719</v>
+        <v>129438295</v>
       </c>
       <c r="B14" t="n">
-        <v>78473</v>
+        <v>91551</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470105</v>
+        <v>470035</v>
       </c>
       <c r="R14" t="n">
-        <v>7023529</v>
+        <v>7023758</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,7 +2069,7 @@
         <v>129436988</v>
       </c>
       <c r="B15" t="n">
-        <v>92536</v>
+        <v>92542</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,45 +2173,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129438250</v>
+        <v>129438342</v>
       </c>
       <c r="B16" t="n">
-        <v>91354</v>
+        <v>98768</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470035</v>
+        <v>470019</v>
       </c>
       <c r="R16" t="n">
-        <v>7023758</v>
+        <v>7023755</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2252,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2262,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,50 +2289,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129436901</v>
+        <v>129438250</v>
       </c>
       <c r="B17" t="n">
-        <v>57730</v>
+        <v>91360</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470084</v>
+        <v>470035</v>
       </c>
       <c r="R17" t="n">
-        <v>7023711</v>
+        <v>7023758</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2359,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2365,12 +2369,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Barkflag på gran</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2397,42 +2396,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129438342</v>
+        <v>129433401</v>
       </c>
       <c r="B18" t="n">
-        <v>98756</v>
+        <v>57895</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2441,13 +2440,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>470019</v>
+        <v>470063</v>
       </c>
       <c r="R18" t="n">
-        <v>7023755</v>
+        <v>7023544</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2476,7 +2475,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2486,7 +2485,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2513,42 +2512,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129433401</v>
+        <v>129438355</v>
       </c>
       <c r="B19" t="n">
-        <v>57890</v>
+        <v>98768</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2557,13 +2556,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>470063</v>
+        <v>470019</v>
       </c>
       <c r="R19" t="n">
-        <v>7023544</v>
+        <v>7023756</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2592,7 +2591,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2602,7 +2601,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2632,7 +2631,7 @@
         <v>129433226</v>
       </c>
       <c r="B20" t="n">
-        <v>91354</v>
+        <v>91360</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2739,7 +2738,7 @@
         <v>129438622</v>
       </c>
       <c r="B21" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,42 +2842,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129438355</v>
+        <v>129432686</v>
       </c>
       <c r="B22" t="n">
-        <v>98756</v>
+        <v>57895</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2887,13 +2886,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>470019</v>
+        <v>469936</v>
       </c>
       <c r="R22" t="n">
-        <v>7023756</v>
+        <v>7023512</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2922,7 +2921,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2932,7 +2931,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2959,10 +2958,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129432686</v>
+        <v>129438563</v>
       </c>
       <c r="B23" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2989,7 +2988,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3003,10 +3002,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469936</v>
+        <v>469981</v>
       </c>
       <c r="R23" t="n">
-        <v>7023512</v>
+        <v>7023772</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3038,7 +3037,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3048,7 +3047,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3075,42 +3074,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129438563</v>
+        <v>129432713</v>
       </c>
       <c r="B24" t="n">
-        <v>57890</v>
+        <v>97639</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3119,13 +3118,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>469981</v>
+        <v>469891</v>
       </c>
       <c r="R24" t="n">
-        <v>7023772</v>
+        <v>7023526</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3154,7 +3153,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3164,7 +3163,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Mkt rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3194,7 +3198,7 @@
         <v>129431892</v>
       </c>
       <c r="B25" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3301,7 +3305,7 @@
         <v>129438443</v>
       </c>
       <c r="B26" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3414,10 +3418,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129432713</v>
+        <v>129438822</v>
       </c>
       <c r="B27" t="n">
-        <v>97627</v>
+        <v>92542</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3425,43 +3429,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>4769</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469891</v>
+        <v>469982</v>
       </c>
       <c r="R27" t="n">
-        <v>7023526</v>
+        <v>7023799</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3493,7 +3488,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3503,12 +3498,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Mkt rikligt</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3535,32 +3525,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129438822</v>
+        <v>129432736</v>
       </c>
       <c r="B28" t="n">
-        <v>92536</v>
+        <v>91587</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3570,10 +3560,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469982</v>
+        <v>469874</v>
       </c>
       <c r="R28" t="n">
-        <v>7023799</v>
+        <v>7023510</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3605,7 +3595,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3615,7 +3605,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3645,7 +3635,7 @@
         <v>129432249</v>
       </c>
       <c r="B29" t="n">
-        <v>92536</v>
+        <v>92542</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3749,54 +3739,41 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129431802</v>
+        <v>129439057</v>
       </c>
       <c r="B30" t="n">
-        <v>57571</v>
+        <v>91607</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102621</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469884</v>
+        <v>470060</v>
       </c>
       <c r="R30" t="n">
-        <v>7023463</v>
+        <v>7023719</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3828,7 +3805,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3838,12 +3815,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:26</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Höstläte.</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3870,10 +3842,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129432736</v>
+        <v>129436692</v>
       </c>
       <c r="B31" t="n">
-        <v>91581</v>
+        <v>91583</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3881,34 +3853,43 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469874</v>
+        <v>470084</v>
       </c>
       <c r="R31" t="n">
-        <v>7023510</v>
+        <v>7023711</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3940,7 +3921,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3950,7 +3931,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3977,30 +3958,34 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129439057</v>
+        <v>129437246</v>
       </c>
       <c r="B32" t="n">
-        <v>91601</v>
+        <v>92542</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4008,10 +3993,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>470060</v>
+        <v>470062</v>
       </c>
       <c r="R32" t="n">
-        <v>7023719</v>
+        <v>7023744</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4043,7 +4028,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4053,7 +4038,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4080,10 +4065,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129436692</v>
+        <v>129432551</v>
       </c>
       <c r="B33" t="n">
-        <v>91577</v>
+        <v>83036</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4091,43 +4076,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>470084</v>
+        <v>469918</v>
       </c>
       <c r="R33" t="n">
-        <v>7023711</v>
+        <v>7023461</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4159,7 +4135,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4169,7 +4145,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På björkstubbe.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4196,10 +4177,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129437246</v>
+        <v>129433427</v>
       </c>
       <c r="B34" t="n">
-        <v>92536</v>
+        <v>98685</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4207,34 +4188,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4769</v>
+        <v>219790</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>470062</v>
+        <v>470059</v>
       </c>
       <c r="R34" t="n">
-        <v>7023744</v>
+        <v>7023547</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4266,7 +4256,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4276,7 +4266,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4303,38 +4293,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129435273</v>
+        <v>129438312</v>
       </c>
       <c r="B35" t="n">
-        <v>57730</v>
+        <v>98768</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4343,10 +4337,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>470105</v>
+        <v>470030</v>
       </c>
       <c r="R35" t="n">
-        <v>7023529</v>
+        <v>7023735</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4378,7 +4372,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4388,7 +4382,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4415,10 +4409,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129432551</v>
+        <v>129433664</v>
       </c>
       <c r="B36" t="n">
-        <v>83031</v>
+        <v>57732</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4426,37 +4420,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>469918</v>
+        <v>470092</v>
       </c>
       <c r="R36" t="n">
-        <v>7023461</v>
+        <v>7023517</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4485,7 +4484,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4495,12 +4494,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På björkstubbe.</t>
+          <t>Bearbetad torraka.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4527,42 +4526,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129433427</v>
+        <v>129437140</v>
       </c>
       <c r="B37" t="n">
-        <v>98673</v>
+        <v>57732</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4571,13 +4566,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>470059</v>
+        <v>470060</v>
       </c>
       <c r="R37" t="n">
-        <v>7023547</v>
+        <v>7023746</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4606,7 +4601,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4616,7 +4611,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4643,42 +4638,47 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129438312</v>
+        <v>129431850</v>
       </c>
       <c r="B38" t="n">
-        <v>98756</v>
+        <v>57895</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4687,10 +4687,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>470030</v>
+        <v>469888</v>
       </c>
       <c r="R38" t="n">
-        <v>7023735</v>
+        <v>7023489</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4759,10 +4759,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129433664</v>
+        <v>129433079</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>78478</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4770,39 +4770,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>470092</v>
+        <v>469974</v>
       </c>
       <c r="R39" t="n">
-        <v>7023517</v>
+        <v>7023561</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4834,7 +4829,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4844,12 +4839,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Bearbetad torraka.</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4876,38 +4866,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129437140</v>
+        <v>129433203</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>105819</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>221725</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4916,13 +4910,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>470060</v>
+        <v>470028</v>
       </c>
       <c r="R40" t="n">
-        <v>7023746</v>
+        <v>7023556</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4951,7 +4945,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4961,7 +4955,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4988,32 +4982,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129431850</v>
+        <v>129431867</v>
       </c>
       <c r="B41" t="n">
-        <v>57890</v>
+        <v>58368</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>102125</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5021,14 +5015,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5043,7 +5032,7 @@
         <v>7023489</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5072,7 +5061,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5082,7 +5071,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Lock.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5109,10 +5103,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129433079</v>
+        <v>129438495</v>
       </c>
       <c r="B42" t="n">
-        <v>78473</v>
+        <v>91587</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5120,21 +5114,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5144,13 +5138,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469974</v>
+        <v>470000</v>
       </c>
       <c r="R42" t="n">
-        <v>7023561</v>
+        <v>7023770</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5179,7 +5173,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5189,7 +5183,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5216,38 +5210,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129438474</v>
+        <v>129432587</v>
       </c>
       <c r="B43" t="n">
-        <v>57730</v>
+        <v>98672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5256,10 +5254,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>469996</v>
+        <v>469915</v>
       </c>
       <c r="R43" t="n">
-        <v>7023753</v>
+        <v>7023493</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5291,7 +5289,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5301,12 +5299,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Barkflag/ringhack</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5333,57 +5326,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129433203</v>
+        <v>129438794</v>
       </c>
       <c r="B44" t="n">
-        <v>105807</v>
+        <v>91587</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221725</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>470028</v>
+        <v>469986</v>
       </c>
       <c r="R44" t="n">
-        <v>7023556</v>
+        <v>7023830</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5412,7 +5396,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5422,7 +5406,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5449,57 +5433,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129431867</v>
+        <v>129437030</v>
       </c>
       <c r="B45" t="n">
-        <v>58363</v>
+        <v>79075</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102125</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>469888</v>
+        <v>470069</v>
       </c>
       <c r="R45" t="n">
-        <v>7023489</v>
+        <v>7023735</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5528,7 +5503,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5538,12 +5513,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Lock.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5570,10 +5540,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129438495</v>
+        <v>129432731</v>
       </c>
       <c r="B46" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5605,10 +5575,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>470000</v>
+        <v>469875</v>
       </c>
       <c r="R46" t="n">
-        <v>7023770</v>
+        <v>7023508</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5640,7 +5610,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5650,7 +5620,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5677,42 +5647,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129432587</v>
+        <v>129436901</v>
       </c>
       <c r="B47" t="n">
-        <v>98660</v>
+        <v>57735</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5721,10 +5687,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>469915</v>
+        <v>470084</v>
       </c>
       <c r="R47" t="n">
-        <v>7023493</v>
+        <v>7023711</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5756,7 +5722,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5766,7 +5732,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Barkflag på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5793,45 +5764,54 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129438794</v>
+        <v>129431802</v>
       </c>
       <c r="B48" t="n">
-        <v>91581</v>
+        <v>57576</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>102621</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>469986</v>
+        <v>469884</v>
       </c>
       <c r="R48" t="n">
-        <v>7023830</v>
+        <v>7023463</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5863,7 +5843,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5873,7 +5853,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Höstläte.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5900,10 +5885,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129437030</v>
+        <v>129435273</v>
       </c>
       <c r="B49" t="n">
-        <v>79070</v>
+        <v>57735</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5911,34 +5896,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>470069</v>
+        <v>470105</v>
       </c>
       <c r="R49" t="n">
-        <v>7023735</v>
+        <v>7023529</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5970,7 +5960,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5980,7 +5970,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6007,10 +5997,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129432731</v>
+        <v>129438474</v>
       </c>
       <c r="B50" t="n">
-        <v>91581</v>
+        <v>57735</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6018,34 +6008,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>469875</v>
+        <v>469996</v>
       </c>
       <c r="R50" t="n">
-        <v>7023508</v>
+        <v>7023753</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6077,7 +6072,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6087,7 +6082,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Barkflag/ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -1852,32 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129433719</v>
+        <v>129438295</v>
       </c>
       <c r="B13" t="n">
-        <v>78478</v>
+        <v>91552</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470105</v>
+        <v>470035</v>
       </c>
       <c r="R13" t="n">
-        <v>7023529</v>
+        <v>7023758</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,32 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129438295</v>
+        <v>129433719</v>
       </c>
       <c r="B14" t="n">
-        <v>91551</v>
+        <v>78479</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470035</v>
+        <v>470105</v>
       </c>
       <c r="R14" t="n">
-        <v>7023758</v>
+        <v>7023529</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,7 +2069,7 @@
         <v>129436988</v>
       </c>
       <c r="B15" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>129438342</v>
       </c>
       <c r="B16" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>129438250</v>
       </c>
       <c r="B17" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>129433401</v>
       </c>
       <c r="B18" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,54 +2512,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129438355</v>
+        <v>129438622</v>
       </c>
       <c r="B19" t="n">
-        <v>98768</v>
+        <v>91552</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>470019</v>
+        <v>469988</v>
       </c>
       <c r="R19" t="n">
-        <v>7023756</v>
+        <v>7023785</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2591,7 +2582,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2601,7 +2592,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2628,48 +2619,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129433226</v>
+        <v>129438355</v>
       </c>
       <c r="B20" t="n">
-        <v>91360</v>
+        <v>98769</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>470038</v>
+        <v>470019</v>
       </c>
       <c r="R20" t="n">
-        <v>7023552</v>
+        <v>7023756</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2735,10 +2735,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129438622</v>
+        <v>129433226</v>
       </c>
       <c r="B21" t="n">
-        <v>91551</v>
+        <v>91361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2746,21 +2746,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>3215</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2770,13 +2770,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469988</v>
+        <v>470038</v>
       </c>
       <c r="R21" t="n">
-        <v>7023785</v>
+        <v>7023552</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2845,7 +2845,7 @@
         <v>129432686</v>
       </c>
       <c r="B22" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>129438563</v>
       </c>
       <c r="B23" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129432713</v>
+        <v>129431892</v>
       </c>
       <c r="B24" t="n">
-        <v>97639</v>
+        <v>91552</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3085,43 +3085,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>469891</v>
+        <v>469888</v>
       </c>
       <c r="R24" t="n">
-        <v>7023526</v>
+        <v>7023489</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3153,7 +3144,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3163,12 +3154,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Mkt rikligt</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3195,10 +3181,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129431892</v>
+        <v>129432713</v>
       </c>
       <c r="B25" t="n">
-        <v>91551</v>
+        <v>97640</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3206,34 +3192,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>469888</v>
+        <v>469891</v>
       </c>
       <c r="R25" t="n">
-        <v>7023489</v>
+        <v>7023526</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3265,7 +3260,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3275,7 +3270,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Mkt rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3305,7 +3305,7 @@
         <v>129438443</v>
       </c>
       <c r="B26" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>129438822</v>
       </c>
       <c r="B27" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3525,32 +3525,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129432736</v>
+        <v>129432249</v>
       </c>
       <c r="B28" t="n">
-        <v>91587</v>
+        <v>92543</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3560,13 +3560,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469874</v>
+        <v>469890</v>
       </c>
       <c r="R28" t="n">
-        <v>7023510</v>
+        <v>7023461</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3632,34 +3632,30 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129432249</v>
+        <v>129439057</v>
       </c>
       <c r="B29" t="n">
-        <v>92542</v>
+        <v>91608</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3667,13 +3663,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469890</v>
+        <v>470060</v>
       </c>
       <c r="R29" t="n">
-        <v>7023461</v>
+        <v>7023719</v>
       </c>
       <c r="S29" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3702,7 +3698,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3712,7 +3708,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3739,10 +3735,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129439057</v>
+        <v>129432736</v>
       </c>
       <c r="B30" t="n">
-        <v>91607</v>
+        <v>91588</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3750,19 +3746,23 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3770,10 +3770,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>470060</v>
+        <v>469874</v>
       </c>
       <c r="R30" t="n">
-        <v>7023719</v>
+        <v>7023510</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3845,7 +3845,7 @@
         <v>129436692</v>
       </c>
       <c r="B31" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>129437246</v>
       </c>
       <c r="B32" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>129432551</v>
       </c>
       <c r="B33" t="n">
-        <v>83036</v>
+        <v>83037</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>129433427</v>
       </c>
       <c r="B34" t="n">
-        <v>98685</v>
+        <v>98686</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>129438312</v>
       </c>
       <c r="B35" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>129433664</v>
       </c>
       <c r="B36" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>129437140</v>
       </c>
       <c r="B37" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4638,10 +4638,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129431850</v>
+        <v>129433079</v>
       </c>
       <c r="B38" t="n">
-        <v>57895</v>
+        <v>78479</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4649,51 +4649,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>469888</v>
+        <v>469974</v>
       </c>
       <c r="R38" t="n">
-        <v>7023489</v>
+        <v>7023561</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4722,7 +4708,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4732,7 +4718,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4759,10 +4745,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129433079</v>
+        <v>129431850</v>
       </c>
       <c r="B39" t="n">
-        <v>78478</v>
+        <v>57896</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4770,37 +4756,51 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>469974</v>
+        <v>469888</v>
       </c>
       <c r="R39" t="n">
-        <v>7023561</v>
+        <v>7023489</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4869,7 +4869,7 @@
         <v>129433203</v>
       </c>
       <c r="B40" t="n">
-        <v>105819</v>
+        <v>105820</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>129431867</v>
       </c>
       <c r="B41" t="n">
-        <v>58368</v>
+        <v>58369</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5103,45 +5103,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129438495</v>
+        <v>129432587</v>
       </c>
       <c r="B42" t="n">
-        <v>91587</v>
+        <v>98673</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>220093</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>470000</v>
+        <v>469915</v>
       </c>
       <c r="R42" t="n">
-        <v>7023770</v>
+        <v>7023493</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5173,7 +5182,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5183,7 +5192,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5210,54 +5219,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129432587</v>
+        <v>129438495</v>
       </c>
       <c r="B43" t="n">
-        <v>98672</v>
+        <v>91588</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220093</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>469915</v>
+        <v>470000</v>
       </c>
       <c r="R43" t="n">
-        <v>7023493</v>
+        <v>7023770</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5326,10 +5326,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129438794</v>
+        <v>129437030</v>
       </c>
       <c r="B44" t="n">
-        <v>91587</v>
+        <v>79076</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5337,21 +5337,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>469986</v>
+        <v>470069</v>
       </c>
       <c r="R44" t="n">
-        <v>7023830</v>
+        <v>7023735</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5433,10 +5433,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129437030</v>
+        <v>129438794</v>
       </c>
       <c r="B45" t="n">
-        <v>79075</v>
+        <v>91588</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>470069</v>
+        <v>469986</v>
       </c>
       <c r="R45" t="n">
-        <v>7023735</v>
+        <v>7023830</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5543,7 +5543,7 @@
         <v>129432731</v>
       </c>
       <c r="B46" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>129436901</v>
       </c>
       <c r="B47" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>129431802</v>
       </c>
       <c r="B48" t="n">
-        <v>57576</v>
+        <v>57577</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>129435273</v>
       </c>
       <c r="B49" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         <v>129438474</v>
       </c>
       <c r="B50" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -2512,10 +2512,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129438622</v>
+        <v>129433226</v>
       </c>
       <c r="B19" t="n">
-        <v>91552</v>
+        <v>91361</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2523,21 +2523,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>3215</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2547,13 +2547,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469988</v>
+        <v>470038</v>
       </c>
       <c r="R19" t="n">
-        <v>7023785</v>
+        <v>7023552</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,54 +2619,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129438355</v>
+        <v>129438622</v>
       </c>
       <c r="B20" t="n">
-        <v>98769</v>
+        <v>91552</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>470019</v>
+        <v>469988</v>
       </c>
       <c r="R20" t="n">
-        <v>7023756</v>
+        <v>7023785</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,7 +2689,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2708,7 +2699,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2735,45 +2726,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129433226</v>
+        <v>129432686</v>
       </c>
       <c r="B21" t="n">
-        <v>91361</v>
+        <v>57896</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3215</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>470038</v>
+        <v>469936</v>
       </c>
       <c r="R21" t="n">
-        <v>7023552</v>
+        <v>7023512</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2842,7 +2842,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129432686</v>
+        <v>129438563</v>
       </c>
       <c r="B22" t="n">
         <v>57896</v>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469936</v>
+        <v>469981</v>
       </c>
       <c r="R22" t="n">
-        <v>7023512</v>
+        <v>7023772</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2958,42 +2958,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129438563</v>
+        <v>129438355</v>
       </c>
       <c r="B23" t="n">
-        <v>57896</v>
+        <v>98769</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3002,13 +3002,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469981</v>
+        <v>470019</v>
       </c>
       <c r="R23" t="n">
-        <v>7023772</v>
+        <v>7023756</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3525,34 +3525,30 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129432249</v>
+        <v>129439057</v>
       </c>
       <c r="B28" t="n">
-        <v>92543</v>
+        <v>91608</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3560,13 +3556,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469890</v>
+        <v>470060</v>
       </c>
       <c r="R28" t="n">
-        <v>7023461</v>
+        <v>7023719</v>
       </c>
       <c r="S28" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3595,7 +3591,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3605,7 +3601,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3632,10 +3628,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129439057</v>
+        <v>129432736</v>
       </c>
       <c r="B29" t="n">
-        <v>91608</v>
+        <v>91588</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3643,19 +3639,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>470060</v>
+        <v>469874</v>
       </c>
       <c r="R29" t="n">
-        <v>7023719</v>
+        <v>7023510</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3735,32 +3735,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129432736</v>
+        <v>129432249</v>
       </c>
       <c r="B30" t="n">
-        <v>91588</v>
+        <v>92543</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3770,13 +3770,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469874</v>
+        <v>469890</v>
       </c>
       <c r="R30" t="n">
-        <v>7023510</v>
+        <v>7023461</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4638,10 +4638,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129433079</v>
+        <v>129431850</v>
       </c>
       <c r="B38" t="n">
-        <v>78479</v>
+        <v>57896</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4649,37 +4649,51 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>469974</v>
+        <v>469888</v>
       </c>
       <c r="R38" t="n">
-        <v>7023561</v>
+        <v>7023489</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4708,7 +4722,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4718,7 +4732,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4745,10 +4759,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129431850</v>
+        <v>129433079</v>
       </c>
       <c r="B39" t="n">
-        <v>57896</v>
+        <v>78479</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4756,51 +4770,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>469888</v>
+        <v>469974</v>
       </c>
       <c r="R39" t="n">
-        <v>7023489</v>
+        <v>7023561</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -1852,32 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129438295</v>
+        <v>129433719</v>
       </c>
       <c r="B13" t="n">
-        <v>91552</v>
+        <v>78484</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470035</v>
+        <v>470105</v>
       </c>
       <c r="R13" t="n">
-        <v>7023758</v>
+        <v>7023529</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,32 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129433719</v>
+        <v>129438295</v>
       </c>
       <c r="B14" t="n">
-        <v>78479</v>
+        <v>91557</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470105</v>
+        <v>470035</v>
       </c>
       <c r="R14" t="n">
-        <v>7023529</v>
+        <v>7023758</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,7 +2069,7 @@
         <v>129436988</v>
       </c>
       <c r="B15" t="n">
-        <v>92543</v>
+        <v>92548</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,54 +2173,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129438342</v>
+        <v>129438250</v>
       </c>
       <c r="B16" t="n">
-        <v>98769</v>
+        <v>91366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470019</v>
+        <v>470035</v>
       </c>
       <c r="R16" t="n">
-        <v>7023755</v>
+        <v>7023758</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2262,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2289,45 +2280,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129438250</v>
+        <v>129438342</v>
       </c>
       <c r="B17" t="n">
-        <v>91361</v>
+        <v>98774</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470035</v>
+        <v>470019</v>
       </c>
       <c r="R17" t="n">
-        <v>7023758</v>
+        <v>7023755</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,48 +2512,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129433226</v>
+        <v>129438355</v>
       </c>
       <c r="B19" t="n">
-        <v>91361</v>
+        <v>98774</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>470038</v>
+        <v>470019</v>
       </c>
       <c r="R19" t="n">
-        <v>7023552</v>
+        <v>7023756</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2582,7 +2591,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2592,7 +2601,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,10 +2628,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129438622</v>
+        <v>129433226</v>
       </c>
       <c r="B20" t="n">
-        <v>91552</v>
+        <v>91366</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,21 +2639,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>3215</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2654,13 +2663,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469988</v>
+        <v>470038</v>
       </c>
       <c r="R20" t="n">
-        <v>7023785</v>
+        <v>7023552</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2689,7 +2698,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2699,7 +2708,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2726,57 +2735,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129432686</v>
+        <v>129438622</v>
       </c>
       <c r="B21" t="n">
-        <v>57896</v>
+        <v>91557</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469936</v>
+        <v>469988</v>
       </c>
       <c r="R21" t="n">
-        <v>7023512</v>
+        <v>7023785</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2842,7 +2842,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129438563</v>
+        <v>129432686</v>
       </c>
       <c r="B22" t="n">
         <v>57896</v>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469981</v>
+        <v>469936</v>
       </c>
       <c r="R22" t="n">
-        <v>7023772</v>
+        <v>7023512</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2958,42 +2958,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129438355</v>
+        <v>129438563</v>
       </c>
       <c r="B23" t="n">
-        <v>98769</v>
+        <v>57896</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3002,13 +3002,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>470019</v>
+        <v>469981</v>
       </c>
       <c r="R23" t="n">
-        <v>7023756</v>
+        <v>7023772</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129431892</v>
+        <v>129432713</v>
       </c>
       <c r="B24" t="n">
-        <v>91552</v>
+        <v>97645</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3085,34 +3085,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>469888</v>
+        <v>469891</v>
       </c>
       <c r="R24" t="n">
-        <v>7023489</v>
+        <v>7023526</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3144,7 +3153,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3154,7 +3163,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Mkt rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3181,10 +3195,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129432713</v>
+        <v>129431892</v>
       </c>
       <c r="B25" t="n">
-        <v>97640</v>
+        <v>91557</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3192,43 +3206,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>469891</v>
+        <v>469888</v>
       </c>
       <c r="R25" t="n">
-        <v>7023526</v>
+        <v>7023489</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3260,7 +3265,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3270,12 +3275,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Mkt rikligt</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3421,7 +3421,7 @@
         <v>129438822</v>
       </c>
       <c r="B27" t="n">
-        <v>92543</v>
+        <v>92548</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>129439057</v>
       </c>
       <c r="B28" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3628,32 +3628,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129432736</v>
+        <v>129432249</v>
       </c>
       <c r="B29" t="n">
-        <v>91588</v>
+        <v>92548</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469874</v>
+        <v>469890</v>
       </c>
       <c r="R29" t="n">
-        <v>7023510</v>
+        <v>7023461</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3735,32 +3735,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129432249</v>
+        <v>129432736</v>
       </c>
       <c r="B30" t="n">
-        <v>92543</v>
+        <v>91593</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3770,13 +3770,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469890</v>
+        <v>469874</v>
       </c>
       <c r="R30" t="n">
-        <v>7023461</v>
+        <v>7023510</v>
       </c>
       <c r="S30" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3845,7 +3845,7 @@
         <v>129436692</v>
       </c>
       <c r="B31" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>129437246</v>
       </c>
       <c r="B32" t="n">
-        <v>92543</v>
+        <v>92548</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>129432551</v>
       </c>
       <c r="B33" t="n">
-        <v>83037</v>
+        <v>83042</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>129433427</v>
       </c>
       <c r="B34" t="n">
-        <v>98686</v>
+        <v>98691</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>129438312</v>
       </c>
       <c r="B35" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129433664</v>
+        <v>129437140</v>
       </c>
       <c r="B36" t="n">
         <v>57733</v>
@@ -4449,13 +4449,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>470092</v>
+        <v>470060</v>
       </c>
       <c r="R36" t="n">
-        <v>7023517</v>
+        <v>7023746</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4494,12 +4494,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Bearbetad torraka.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4526,7 +4521,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129437140</v>
+        <v>129433664</v>
       </c>
       <c r="B37" t="n">
         <v>57733</v>
@@ -4566,13 +4561,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>470060</v>
+        <v>470092</v>
       </c>
       <c r="R37" t="n">
-        <v>7023746</v>
+        <v>7023517</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4601,7 +4596,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4611,7 +4606,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Bearbetad torraka.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4638,10 +4638,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129431850</v>
+        <v>129433079</v>
       </c>
       <c r="B38" t="n">
-        <v>57896</v>
+        <v>78484</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4649,51 +4649,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>469888</v>
+        <v>469974</v>
       </c>
       <c r="R38" t="n">
-        <v>7023489</v>
+        <v>7023561</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4722,7 +4708,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4732,7 +4718,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4759,10 +4745,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129433079</v>
+        <v>129431850</v>
       </c>
       <c r="B39" t="n">
-        <v>78479</v>
+        <v>57896</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4770,37 +4756,51 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>469974</v>
+        <v>469888</v>
       </c>
       <c r="R39" t="n">
-        <v>7023561</v>
+        <v>7023489</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4869,7 +4869,7 @@
         <v>129433203</v>
       </c>
       <c r="B40" t="n">
-        <v>105820</v>
+        <v>105825</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>129432587</v>
       </c>
       <c r="B42" t="n">
-        <v>98673</v>
+        <v>98678</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>129438495</v>
       </c>
       <c r="B43" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5326,10 +5326,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129437030</v>
+        <v>129438794</v>
       </c>
       <c r="B44" t="n">
-        <v>79076</v>
+        <v>91593</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5337,21 +5337,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>470069</v>
+        <v>469986</v>
       </c>
       <c r="R44" t="n">
-        <v>7023735</v>
+        <v>7023830</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5433,10 +5433,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129438794</v>
+        <v>129437030</v>
       </c>
       <c r="B45" t="n">
-        <v>91588</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>469986</v>
+        <v>470069</v>
       </c>
       <c r="R45" t="n">
-        <v>7023830</v>
+        <v>7023735</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5543,7 +5543,7 @@
         <v>129432731</v>
       </c>
       <c r="B46" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -1852,32 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129433719</v>
+        <v>129438295</v>
       </c>
       <c r="B13" t="n">
-        <v>78484</v>
+        <v>91557</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470105</v>
+        <v>470035</v>
       </c>
       <c r="R13" t="n">
-        <v>7023529</v>
+        <v>7023758</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,32 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129438295</v>
+        <v>129433719</v>
       </c>
       <c r="B14" t="n">
-        <v>91557</v>
+        <v>78484</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470035</v>
+        <v>470105</v>
       </c>
       <c r="R14" t="n">
-        <v>7023758</v>
+        <v>7023529</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,45 +2173,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129438250</v>
+        <v>129438342</v>
       </c>
       <c r="B16" t="n">
-        <v>91366</v>
+        <v>98774</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470035</v>
+        <v>470019</v>
       </c>
       <c r="R16" t="n">
-        <v>7023758</v>
+        <v>7023755</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2252,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2262,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,54 +2289,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129438342</v>
+        <v>129438250</v>
       </c>
       <c r="B17" t="n">
-        <v>98774</v>
+        <v>91366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470019</v>
+        <v>470035</v>
       </c>
       <c r="R17" t="n">
-        <v>7023755</v>
+        <v>7023758</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,42 +2512,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129438355</v>
+        <v>129432686</v>
       </c>
       <c r="B19" t="n">
-        <v>98774</v>
+        <v>57896</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2556,13 +2556,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>470019</v>
+        <v>469936</v>
       </c>
       <c r="R19" t="n">
-        <v>7023756</v>
+        <v>7023512</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2628,45 +2628,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129433226</v>
+        <v>129438563</v>
       </c>
       <c r="B20" t="n">
-        <v>91366</v>
+        <v>57896</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3215</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>470038</v>
+        <v>469981</v>
       </c>
       <c r="R20" t="n">
-        <v>7023552</v>
+        <v>7023772</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2698,7 +2707,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2708,7 +2717,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2735,45 +2744,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129438622</v>
+        <v>129438355</v>
       </c>
       <c r="B21" t="n">
-        <v>91557</v>
+        <v>98774</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469988</v>
+        <v>470019</v>
       </c>
       <c r="R21" t="n">
-        <v>7023785</v>
+        <v>7023756</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,7 +2823,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2815,7 +2833,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2842,54 +2860,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129432686</v>
+        <v>129433226</v>
       </c>
       <c r="B22" t="n">
-        <v>57896</v>
+        <v>91366</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>3215</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469936</v>
+        <v>470038</v>
       </c>
       <c r="R22" t="n">
-        <v>7023512</v>
+        <v>7023552</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2921,7 +2930,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2931,7 +2940,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2958,57 +2967,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129438563</v>
+        <v>129438622</v>
       </c>
       <c r="B23" t="n">
-        <v>57896</v>
+        <v>91557</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469981</v>
+        <v>469988</v>
       </c>
       <c r="R23" t="n">
-        <v>7023772</v>
+        <v>7023785</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129432713</v>
+        <v>129431892</v>
       </c>
       <c r="B24" t="n">
-        <v>97645</v>
+        <v>91557</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3085,43 +3085,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>469891</v>
+        <v>469888</v>
       </c>
       <c r="R24" t="n">
-        <v>7023526</v>
+        <v>7023489</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3153,7 +3144,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3163,12 +3154,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Mkt rikligt</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3195,45 +3181,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129431892</v>
+        <v>129438443</v>
       </c>
       <c r="B25" t="n">
-        <v>91557</v>
+        <v>57896</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>469888</v>
+        <v>469996</v>
       </c>
       <c r="R25" t="n">
-        <v>7023489</v>
+        <v>7023753</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3265,7 +3260,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3275,7 +3270,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3302,42 +3297,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129438443</v>
+        <v>129432713</v>
       </c>
       <c r="B26" t="n">
-        <v>57896</v>
+        <v>97645</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3346,10 +3341,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>469996</v>
+        <v>469891</v>
       </c>
       <c r="R26" t="n">
-        <v>7023753</v>
+        <v>7023526</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3381,7 +3376,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3391,7 +3386,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Mkt rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3525,10 +3525,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129439057</v>
+        <v>129432736</v>
       </c>
       <c r="B28" t="n">
-        <v>91613</v>
+        <v>91593</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3536,19 +3536,23 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3556,10 +3560,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>470060</v>
+        <v>469874</v>
       </c>
       <c r="R28" t="n">
-        <v>7023719</v>
+        <v>7023510</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3591,7 +3595,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3601,7 +3605,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3735,10 +3739,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129432736</v>
+        <v>129439057</v>
       </c>
       <c r="B30" t="n">
-        <v>91593</v>
+        <v>91613</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3746,23 +3750,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3770,10 +3770,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469874</v>
+        <v>470060</v>
       </c>
       <c r="R30" t="n">
-        <v>7023510</v>
+        <v>7023719</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4409,7 +4409,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129437140</v>
+        <v>129433664</v>
       </c>
       <c r="B36" t="n">
         <v>57733</v>
@@ -4449,13 +4449,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>470060</v>
+        <v>470092</v>
       </c>
       <c r="R36" t="n">
-        <v>7023746</v>
+        <v>7023517</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4494,7 +4494,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Bearbetad torraka.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4521,7 +4526,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129433664</v>
+        <v>129437140</v>
       </c>
       <c r="B37" t="n">
         <v>57733</v>
@@ -4561,13 +4566,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>470092</v>
+        <v>470060</v>
       </c>
       <c r="R37" t="n">
-        <v>7023517</v>
+        <v>7023746</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4596,7 +4601,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4606,12 +4611,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Bearbetad torraka.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5103,54 +5103,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129432587</v>
+        <v>129438495</v>
       </c>
       <c r="B42" t="n">
-        <v>98678</v>
+        <v>91593</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220093</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469915</v>
+        <v>470000</v>
       </c>
       <c r="R42" t="n">
-        <v>7023493</v>
+        <v>7023770</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5182,7 +5173,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5192,7 +5183,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5219,45 +5210,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129438495</v>
+        <v>129432587</v>
       </c>
       <c r="B43" t="n">
-        <v>91593</v>
+        <v>98678</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220093</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>470000</v>
+        <v>469915</v>
       </c>
       <c r="R43" t="n">
-        <v>7023770</v>
+        <v>7023493</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -2512,42 +2512,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129432686</v>
+        <v>129438355</v>
       </c>
       <c r="B19" t="n">
-        <v>57896</v>
+        <v>98774</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2556,13 +2556,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469936</v>
+        <v>470019</v>
       </c>
       <c r="R19" t="n">
-        <v>7023512</v>
+        <v>7023756</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2628,54 +2628,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129438563</v>
+        <v>129433226</v>
       </c>
       <c r="B20" t="n">
-        <v>57896</v>
+        <v>91366</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>3215</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469981</v>
+        <v>470038</v>
       </c>
       <c r="R20" t="n">
-        <v>7023772</v>
+        <v>7023552</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2707,7 +2698,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2717,7 +2708,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2744,54 +2735,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129438355</v>
+        <v>129438622</v>
       </c>
       <c r="B21" t="n">
-        <v>98774</v>
+        <v>91557</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>470019</v>
+        <v>469988</v>
       </c>
       <c r="R21" t="n">
-        <v>7023756</v>
+        <v>7023785</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2823,7 +2805,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2833,7 +2815,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2860,45 +2842,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129433226</v>
+        <v>129432686</v>
       </c>
       <c r="B22" t="n">
-        <v>91366</v>
+        <v>57896</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3215</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>470038</v>
+        <v>469936</v>
       </c>
       <c r="R22" t="n">
-        <v>7023552</v>
+        <v>7023512</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2930,7 +2921,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2940,7 +2931,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2967,48 +2958,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129438622</v>
+        <v>129438563</v>
       </c>
       <c r="B23" t="n">
-        <v>91557</v>
+        <v>57896</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469988</v>
+        <v>469981</v>
       </c>
       <c r="R23" t="n">
-        <v>7023785</v>
+        <v>7023772</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3632,34 +3632,30 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129432249</v>
+        <v>129439057</v>
       </c>
       <c r="B29" t="n">
-        <v>92548</v>
+        <v>91613</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3667,13 +3663,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469890</v>
+        <v>470060</v>
       </c>
       <c r="R29" t="n">
-        <v>7023461</v>
+        <v>7023719</v>
       </c>
       <c r="S29" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3702,7 +3698,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3712,7 +3708,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3739,30 +3735,34 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129439057</v>
+        <v>129432249</v>
       </c>
       <c r="B30" t="n">
-        <v>91613</v>
+        <v>92548</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3770,13 +3770,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>470060</v>
+        <v>469890</v>
       </c>
       <c r="R30" t="n">
-        <v>7023719</v>
+        <v>7023461</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -5326,10 +5326,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129438794</v>
+        <v>129437030</v>
       </c>
       <c r="B44" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5337,21 +5337,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>469986</v>
+        <v>470069</v>
       </c>
       <c r="R44" t="n">
-        <v>7023830</v>
+        <v>7023735</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5433,10 +5433,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129437030</v>
+        <v>129438794</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>470069</v>
+        <v>469986</v>
       </c>
       <c r="R45" t="n">
-        <v>7023735</v>
+        <v>7023830</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -2512,42 +2512,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129438355</v>
+        <v>129438563</v>
       </c>
       <c r="B19" t="n">
-        <v>98774</v>
+        <v>57896</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2556,13 +2556,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>470019</v>
+        <v>469981</v>
       </c>
       <c r="R19" t="n">
-        <v>7023756</v>
+        <v>7023772</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2958,42 +2958,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129438563</v>
+        <v>129438355</v>
       </c>
       <c r="B23" t="n">
-        <v>57896</v>
+        <v>98774</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3002,13 +3002,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469981</v>
+        <v>470019</v>
       </c>
       <c r="R23" t="n">
-        <v>7023772</v>
+        <v>7023756</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4638,10 +4638,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129433079</v>
+        <v>129431850</v>
       </c>
       <c r="B38" t="n">
-        <v>78484</v>
+        <v>57896</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4649,37 +4649,51 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>469974</v>
+        <v>469888</v>
       </c>
       <c r="R38" t="n">
-        <v>7023561</v>
+        <v>7023489</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4708,7 +4722,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4718,7 +4732,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4745,10 +4759,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129431850</v>
+        <v>129433079</v>
       </c>
       <c r="B39" t="n">
-        <v>57896</v>
+        <v>78484</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4756,51 +4770,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>469888</v>
+        <v>469974</v>
       </c>
       <c r="R39" t="n">
-        <v>7023489</v>
+        <v>7023561</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5326,10 +5326,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129437030</v>
+        <v>129438794</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5337,21 +5337,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>470069</v>
+        <v>469986</v>
       </c>
       <c r="R44" t="n">
-        <v>7023735</v>
+        <v>7023830</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5433,10 +5433,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129438794</v>
+        <v>129437030</v>
       </c>
       <c r="B45" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>469986</v>
+        <v>470069</v>
       </c>
       <c r="R45" t="n">
-        <v>7023830</v>
+        <v>7023735</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -1852,32 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129438295</v>
+        <v>129433719</v>
       </c>
       <c r="B13" t="n">
-        <v>91557</v>
+        <v>78484</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470035</v>
+        <v>470105</v>
       </c>
       <c r="R13" t="n">
-        <v>7023758</v>
+        <v>7023529</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,32 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129433719</v>
+        <v>129438295</v>
       </c>
       <c r="B14" t="n">
-        <v>78484</v>
+        <v>91561</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470105</v>
+        <v>470035</v>
       </c>
       <c r="R14" t="n">
-        <v>7023529</v>
+        <v>7023758</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,7 +2069,7 @@
         <v>129436988</v>
       </c>
       <c r="B15" t="n">
-        <v>92548</v>
+        <v>92552</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,54 +2173,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129438342</v>
+        <v>129438250</v>
       </c>
       <c r="B16" t="n">
-        <v>98774</v>
+        <v>91370</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470019</v>
+        <v>470035</v>
       </c>
       <c r="R16" t="n">
-        <v>7023755</v>
+        <v>7023758</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2262,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2289,45 +2280,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129438250</v>
+        <v>129438342</v>
       </c>
       <c r="B17" t="n">
-        <v>91366</v>
+        <v>98778</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470035</v>
+        <v>470019</v>
       </c>
       <c r="R17" t="n">
-        <v>7023758</v>
+        <v>7023755</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,54 +2512,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129438563</v>
+        <v>129433226</v>
       </c>
       <c r="B19" t="n">
-        <v>57896</v>
+        <v>91370</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>3215</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469981</v>
+        <v>470038</v>
       </c>
       <c r="R19" t="n">
-        <v>7023772</v>
+        <v>7023552</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2591,7 +2582,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2601,7 +2592,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2628,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129433226</v>
+        <v>129438622</v>
       </c>
       <c r="B20" t="n">
-        <v>91366</v>
+        <v>91561</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2639,21 +2630,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3215</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2663,13 +2654,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>470038</v>
+        <v>469988</v>
       </c>
       <c r="R20" t="n">
-        <v>7023552</v>
+        <v>7023785</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2698,7 +2689,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2708,7 +2699,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2735,48 +2726,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129438622</v>
+        <v>129432686</v>
       </c>
       <c r="B21" t="n">
-        <v>91557</v>
+        <v>57896</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469988</v>
+        <v>469936</v>
       </c>
       <c r="R21" t="n">
-        <v>7023785</v>
+        <v>7023512</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2842,7 +2842,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129432686</v>
+        <v>129438563</v>
       </c>
       <c r="B22" t="n">
         <v>57896</v>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469936</v>
+        <v>469981</v>
       </c>
       <c r="R22" t="n">
-        <v>7023512</v>
+        <v>7023772</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2961,7 +2961,7 @@
         <v>129438355</v>
       </c>
       <c r="B23" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>129431892</v>
       </c>
       <c r="B24" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>129432713</v>
       </c>
       <c r="B26" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>129438822</v>
       </c>
       <c r="B27" t="n">
-        <v>92548</v>
+        <v>92552</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3525,10 +3525,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129432736</v>
+        <v>129439057</v>
       </c>
       <c r="B28" t="n">
-        <v>91593</v>
+        <v>91617</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3536,23 +3536,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3560,10 +3556,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469874</v>
+        <v>470060</v>
       </c>
       <c r="R28" t="n">
-        <v>7023510</v>
+        <v>7023719</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3595,7 +3591,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3605,7 +3601,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3632,30 +3628,34 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129439057</v>
+        <v>129432249</v>
       </c>
       <c r="B29" t="n">
-        <v>91613</v>
+        <v>92552</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>470060</v>
+        <v>469890</v>
       </c>
       <c r="R29" t="n">
-        <v>7023719</v>
+        <v>7023461</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3735,32 +3735,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129432249</v>
+        <v>129432736</v>
       </c>
       <c r="B30" t="n">
-        <v>92548</v>
+        <v>91597</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3770,13 +3770,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469890</v>
+        <v>469874</v>
       </c>
       <c r="R30" t="n">
-        <v>7023461</v>
+        <v>7023510</v>
       </c>
       <c r="S30" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3845,7 +3845,7 @@
         <v>129436692</v>
       </c>
       <c r="B31" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>129437246</v>
       </c>
       <c r="B32" t="n">
-        <v>92548</v>
+        <v>92552</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>129433427</v>
       </c>
       <c r="B34" t="n">
-        <v>98691</v>
+        <v>98695</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>129438312</v>
       </c>
       <c r="B35" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>129433203</v>
       </c>
       <c r="B40" t="n">
-        <v>105825</v>
+        <v>105829</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>129438495</v>
       </c>
       <c r="B42" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>129432587</v>
       </c>
       <c r="B43" t="n">
-        <v>98678</v>
+        <v>98682</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>129438794</v>
       </c>
       <c r="B44" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>129432731</v>
       </c>
       <c r="B46" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -1962,7 +1962,7 @@
         <v>129438295</v>
       </c>
       <c r="B14" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>129436988</v>
       </c>
       <c r="B15" t="n">
-        <v>92552</v>
+        <v>92554</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>129438250</v>
       </c>
       <c r="B16" t="n">
-        <v>91370</v>
+        <v>91372</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>129438342</v>
       </c>
       <c r="B17" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>129433226</v>
       </c>
       <c r="B19" t="n">
-        <v>91370</v>
+        <v>91372</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>129438622</v>
       </c>
       <c r="B20" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>129438355</v>
       </c>
       <c r="B23" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3074,45 +3074,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129431892</v>
+        <v>129438443</v>
       </c>
       <c r="B24" t="n">
-        <v>91561</v>
+        <v>57896</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>469888</v>
+        <v>469996</v>
       </c>
       <c r="R24" t="n">
-        <v>7023489</v>
+        <v>7023753</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3144,7 +3153,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3154,7 +3163,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3181,54 +3190,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129438443</v>
+        <v>129431892</v>
       </c>
       <c r="B25" t="n">
-        <v>57896</v>
+        <v>91563</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>469996</v>
+        <v>469888</v>
       </c>
       <c r="R25" t="n">
-        <v>7023753</v>
+        <v>7023489</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3300,7 +3300,7 @@
         <v>129432713</v>
       </c>
       <c r="B26" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>129438822</v>
       </c>
       <c r="B27" t="n">
-        <v>92552</v>
+        <v>92554</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3525,10 +3525,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129439057</v>
+        <v>129432736</v>
       </c>
       <c r="B28" t="n">
-        <v>91617</v>
+        <v>91599</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3536,19 +3536,23 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3556,10 +3560,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>470060</v>
+        <v>469874</v>
       </c>
       <c r="R28" t="n">
-        <v>7023719</v>
+        <v>7023510</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3591,7 +3595,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3601,7 +3605,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3628,34 +3632,30 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129432249</v>
+        <v>129439057</v>
       </c>
       <c r="B29" t="n">
-        <v>92552</v>
+        <v>91619</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469890</v>
+        <v>470060</v>
       </c>
       <c r="R29" t="n">
-        <v>7023461</v>
+        <v>7023719</v>
       </c>
       <c r="S29" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3735,32 +3735,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129432736</v>
+        <v>129432249</v>
       </c>
       <c r="B30" t="n">
-        <v>91597</v>
+        <v>92554</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3770,13 +3770,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469874</v>
+        <v>469890</v>
       </c>
       <c r="R30" t="n">
-        <v>7023510</v>
+        <v>7023461</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3842,54 +3842,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129436692</v>
+        <v>129437246</v>
       </c>
       <c r="B31" t="n">
-        <v>91593</v>
+        <v>92554</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>470084</v>
+        <v>470062</v>
       </c>
       <c r="R31" t="n">
-        <v>7023711</v>
+        <v>7023744</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3921,7 +3912,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3931,7 +3922,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3958,45 +3949,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129437246</v>
+        <v>129436692</v>
       </c>
       <c r="B32" t="n">
-        <v>92552</v>
+        <v>91595</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>470062</v>
+        <v>470084</v>
       </c>
       <c r="R32" t="n">
-        <v>7023744</v>
+        <v>7023711</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4068,7 +4068,7 @@
         <v>129432551</v>
       </c>
       <c r="B33" t="n">
-        <v>83042</v>
+        <v>83044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>129433427</v>
       </c>
       <c r="B34" t="n">
-        <v>98695</v>
+        <v>98697</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>129438312</v>
       </c>
       <c r="B35" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4638,10 +4638,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129431850</v>
+        <v>129433079</v>
       </c>
       <c r="B38" t="n">
-        <v>57896</v>
+        <v>78484</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4649,51 +4649,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>469888</v>
+        <v>469974</v>
       </c>
       <c r="R38" t="n">
-        <v>7023489</v>
+        <v>7023561</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4722,7 +4708,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4732,7 +4718,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4759,10 +4745,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129433079</v>
+        <v>129431850</v>
       </c>
       <c r="B39" t="n">
-        <v>78484</v>
+        <v>57896</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4770,37 +4756,51 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>469974</v>
+        <v>469888</v>
       </c>
       <c r="R39" t="n">
-        <v>7023561</v>
+        <v>7023489</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4869,7 +4869,7 @@
         <v>129433203</v>
       </c>
       <c r="B40" t="n">
-        <v>105829</v>
+        <v>105831</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>129438495</v>
       </c>
       <c r="B42" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>129432587</v>
       </c>
       <c r="B43" t="n">
-        <v>98682</v>
+        <v>98684</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>129438794</v>
       </c>
       <c r="B44" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>129432731</v>
       </c>
       <c r="B46" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -2173,45 +2173,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129438250</v>
+        <v>129438342</v>
       </c>
       <c r="B16" t="n">
-        <v>91372</v>
+        <v>98780</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470035</v>
+        <v>470019</v>
       </c>
       <c r="R16" t="n">
-        <v>7023758</v>
+        <v>7023755</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2252,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2262,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,54 +2289,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129438342</v>
+        <v>129438250</v>
       </c>
       <c r="B17" t="n">
-        <v>98780</v>
+        <v>91372</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470019</v>
+        <v>470035</v>
       </c>
       <c r="R17" t="n">
-        <v>7023755</v>
+        <v>7023758</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2619,48 +2619,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129438622</v>
+        <v>129432686</v>
       </c>
       <c r="B20" t="n">
-        <v>91563</v>
+        <v>57896</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469988</v>
+        <v>469936</v>
       </c>
       <c r="R20" t="n">
-        <v>7023785</v>
+        <v>7023512</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2689,7 +2698,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2699,7 +2708,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2726,7 +2735,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129432686</v>
+        <v>129438563</v>
       </c>
       <c r="B21" t="n">
         <v>57896</v>
@@ -2756,7 +2765,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2770,10 +2779,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469936</v>
+        <v>469981</v>
       </c>
       <c r="R21" t="n">
-        <v>7023512</v>
+        <v>7023772</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2805,7 +2814,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2815,7 +2824,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2842,57 +2851,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129438563</v>
+        <v>129438622</v>
       </c>
       <c r="B22" t="n">
-        <v>57896</v>
+        <v>91563</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469981</v>
+        <v>469988</v>
       </c>
       <c r="R22" t="n">
-        <v>7023772</v>
+        <v>7023785</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3074,42 +3074,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129438443</v>
+        <v>129432713</v>
       </c>
       <c r="B24" t="n">
-        <v>57896</v>
+        <v>97651</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>469996</v>
+        <v>469891</v>
       </c>
       <c r="R24" t="n">
-        <v>7023753</v>
+        <v>7023526</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3163,7 +3163,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Mkt rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3297,42 +3302,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129432713</v>
+        <v>129438443</v>
       </c>
       <c r="B26" t="n">
-        <v>97651</v>
+        <v>57896</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3341,10 +3346,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>469891</v>
+        <v>469996</v>
       </c>
       <c r="R26" t="n">
-        <v>7023526</v>
+        <v>7023753</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3376,7 +3381,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3386,12 +3391,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Mkt rikligt</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -5326,10 +5326,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129438794</v>
+        <v>129437030</v>
       </c>
       <c r="B44" t="n">
-        <v>91599</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5337,21 +5337,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>469986</v>
+        <v>470069</v>
       </c>
       <c r="R44" t="n">
-        <v>7023830</v>
+        <v>7023735</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5433,10 +5433,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129437030</v>
+        <v>129438794</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>470069</v>
+        <v>469986</v>
       </c>
       <c r="R45" t="n">
-        <v>7023735</v>
+        <v>7023830</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -3525,10 +3525,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129432736</v>
+        <v>129439057</v>
       </c>
       <c r="B28" t="n">
-        <v>91599</v>
+        <v>91619</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3536,23 +3536,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3560,10 +3556,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469874</v>
+        <v>470060</v>
       </c>
       <c r="R28" t="n">
-        <v>7023510</v>
+        <v>7023719</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3595,7 +3591,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3605,7 +3601,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3632,30 +3628,34 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129439057</v>
+        <v>129432249</v>
       </c>
       <c r="B29" t="n">
-        <v>91619</v>
+        <v>92554</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>470060</v>
+        <v>469890</v>
       </c>
       <c r="R29" t="n">
-        <v>7023719</v>
+        <v>7023461</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3735,32 +3735,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129432249</v>
+        <v>129432736</v>
       </c>
       <c r="B30" t="n">
-        <v>92554</v>
+        <v>91599</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3770,13 +3770,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469890</v>
+        <v>469874</v>
       </c>
       <c r="R30" t="n">
-        <v>7023461</v>
+        <v>7023510</v>
       </c>
       <c r="S30" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3842,45 +3842,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129437246</v>
+        <v>129436692</v>
       </c>
       <c r="B31" t="n">
-        <v>92554</v>
+        <v>91595</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>470062</v>
+        <v>470084</v>
       </c>
       <c r="R31" t="n">
-        <v>7023744</v>
+        <v>7023711</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3912,7 +3921,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3922,7 +3931,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3949,54 +3958,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129436692</v>
+        <v>129437246</v>
       </c>
       <c r="B32" t="n">
-        <v>91595</v>
+        <v>92554</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svintjärnflon, Svintjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>470084</v>
+        <v>470062</v>
       </c>
       <c r="R32" t="n">
-        <v>7023711</v>
+        <v>7023744</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -5650,7 +5650,7 @@
         <v>129436901</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>129431802</v>
       </c>
       <c r="B48" t="n">
-        <v>57577</v>
+        <v>57578</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>129435273</v>
       </c>
       <c r="B49" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         <v>129438474</v>
       </c>
       <c r="B50" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 51998-2025 artfynd.xlsx
+++ b/artfynd/A 51998-2025 artfynd.xlsx
@@ -5650,7 +5650,7 @@
         <v>129436901</v>
       </c>
       <c r="B47" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>129431802</v>
       </c>
       <c r="B48" t="n">
-        <v>57578</v>
+        <v>57581</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>129435273</v>
       </c>
       <c r="B49" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         <v>129438474</v>
       </c>
       <c r="B50" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
